--- a/List_of_crops_update_all_3.xlsx
+++ b/List_of_crops_update_all_3.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GIT\antigravity\Land cover\github\Land-cover-validation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5359F5E2-0514-465E-97EF-D685B86B6202}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BAE4D40-CA25-4100-A52A-EF5E5FC49B12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="770" yWindow="4280" windowWidth="23230" windowHeight="10180" xr2:uid="{ADA269A6-2ED3-4A77-8230-6F13C182E555}"/>
+    <workbookView xWindow="19110" yWindow="0" windowWidth="19380" windowHeight="20970" activeTab="4" xr2:uid="{ADA269A6-2ED3-4A77-8230-6F13C182E555}"/>
   </bookViews>
   <sheets>
     <sheet name="Crop_list_HND" sheetId="8" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1494" uniqueCount="282">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1524" uniqueCount="291">
   <si>
     <t>Level_1</t>
   </si>
@@ -892,13 +892,40 @@
   </si>
   <si>
     <t>Artificial waterbody</t>
+  </si>
+  <si>
+    <t>Dryland rice</t>
+  </si>
+  <si>
+    <t>Monkeynuts</t>
+  </si>
+  <si>
+    <t>Pineapples</t>
+  </si>
+  <si>
+    <t>Greenhouses</t>
+  </si>
+  <si>
+    <t>Sisal</t>
+  </si>
+  <si>
+    <t>Snow</t>
+  </si>
+  <si>
+    <t>Salt pans</t>
+  </si>
+  <si>
+    <t>Ocean</t>
+  </si>
+  <si>
+    <t>Vegetated Wetlands</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -968,8 +995,15 @@
       <color rgb="FF000000"/>
       <name val="Aptos"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="13">
+  <fills count="14">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1042,8 +1076,14 @@
         <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="9">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -1147,11 +1187,22 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1194,6 +1245,18 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4381,7 +4444,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F421573-7F45-40AE-9E4F-984A0D6DDEFC}">
-  <dimension ref="A1:C88"/>
+  <dimension ref="A1:C98"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="33.26953125" customWidth="1"/>
@@ -4404,10 +4467,10 @@
       <c r="A2" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="32" t="s">
         <v>63</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="32" t="s">
         <v>155</v>
       </c>
     </row>
@@ -4415,10 +4478,10 @@
       <c r="A3" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="32" t="s">
         <v>63</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="32" t="s">
         <v>79</v>
       </c>
     </row>
@@ -4426,10 +4489,10 @@
       <c r="A4" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="32" t="s">
         <v>120</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="32" t="s">
         <v>121</v>
       </c>
     </row>
@@ -4437,10 +4500,10 @@
       <c r="A5" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="32" t="s">
         <v>120</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="32" t="s">
         <v>156</v>
       </c>
     </row>
@@ -4448,10 +4511,10 @@
       <c r="A6" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="32" t="s">
         <v>120</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="32" t="s">
         <v>123</v>
       </c>
     </row>
@@ -4459,10 +4522,10 @@
       <c r="A7" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="32" t="s">
         <v>120</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" s="32" t="s">
         <v>79</v>
       </c>
     </row>
@@ -4470,10 +4533,10 @@
       <c r="A8" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="C8" s="2" t="s">
+      <c r="B8" s="32" t="s">
+        <v>79</v>
+      </c>
+      <c r="C8" s="32" t="s">
         <v>79</v>
       </c>
     </row>
@@ -4481,10 +4544,10 @@
       <c r="A9" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="32" t="s">
         <v>157</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="C9" s="32" t="s">
         <v>157</v>
       </c>
     </row>
@@ -4492,10 +4555,10 @@
       <c r="A10" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="32" t="s">
         <v>157</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="C10" s="32" t="s">
         <v>79</v>
       </c>
     </row>
@@ -4503,10 +4566,10 @@
       <c r="A11" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="32" t="s">
         <v>158</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="C11" s="32" t="s">
         <v>158</v>
       </c>
     </row>
@@ -4514,10 +4577,10 @@
       <c r="A12" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="32" t="s">
         <v>158</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="C12" s="32" t="s">
         <v>79</v>
       </c>
     </row>
@@ -4525,10 +4588,10 @@
       <c r="A13" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="B13" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="C13" s="2" t="s">
+      <c r="B13" s="32" t="s">
+        <v>79</v>
+      </c>
+      <c r="C13" s="32" t="s">
         <v>79</v>
       </c>
     </row>
@@ -4536,10 +4599,10 @@
       <c r="A14" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="B14" s="32" t="s">
         <v>159</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="C14" s="32" t="s">
         <v>159</v>
       </c>
     </row>
@@ -4547,10 +4610,10 @@
       <c r="A15" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="B15" s="32" t="s">
         <v>124</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="C15" s="32" t="s">
         <v>124</v>
       </c>
     </row>
@@ -4558,10 +4621,10 @@
       <c r="A16" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="B16" s="32" t="s">
         <v>125</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="C16" s="32" t="s">
         <v>125</v>
       </c>
     </row>
@@ -4569,10 +4632,10 @@
       <c r="A17" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="B17" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="C17" s="2" t="s">
+      <c r="B17" s="32" t="s">
+        <v>79</v>
+      </c>
+      <c r="C17" s="32" t="s">
         <v>79</v>
       </c>
     </row>
@@ -4580,7 +4643,7 @@
       <c r="A18" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B18" s="2" t="s">
+      <c r="B18" s="32" t="s">
         <v>92</v>
       </c>
       <c r="C18" s="3" t="s">
@@ -4591,7 +4654,7 @@
       <c r="A19" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B19" s="2" t="s">
+      <c r="B19" s="32" t="s">
         <v>92</v>
       </c>
       <c r="C19" s="3" t="s">
@@ -4602,7 +4665,7 @@
       <c r="A20" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B20" s="2" t="s">
+      <c r="B20" s="32" t="s">
         <v>92</v>
       </c>
       <c r="C20" s="3" t="s">
@@ -4613,7 +4676,7 @@
       <c r="A21" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B21" s="2" t="s">
+      <c r="B21" s="32" t="s">
         <v>92</v>
       </c>
       <c r="C21" s="3" t="s">
@@ -4624,7 +4687,7 @@
       <c r="A22" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B22" s="2" t="s">
+      <c r="B22" s="32" t="s">
         <v>92</v>
       </c>
       <c r="C22" s="3" t="s">
@@ -4635,7 +4698,7 @@
       <c r="A23" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B23" s="2" t="s">
+      <c r="B23" s="32" t="s">
         <v>92</v>
       </c>
       <c r="C23" s="3" t="s">
@@ -4646,7 +4709,7 @@
       <c r="A24" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B24" s="2" t="s">
+      <c r="B24" s="32" t="s">
         <v>92</v>
       </c>
       <c r="C24" s="3" t="s">
@@ -4657,7 +4720,7 @@
       <c r="A25" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B25" s="2" t="s">
+      <c r="B25" s="32" t="s">
         <v>92</v>
       </c>
       <c r="C25" s="3" t="s">
@@ -4668,7 +4731,7 @@
       <c r="A26" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B26" s="2" t="s">
+      <c r="B26" s="32" t="s">
         <v>92</v>
       </c>
       <c r="C26" s="3" t="s">
@@ -4679,7 +4742,7 @@
       <c r="A27" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B27" s="2" t="s">
+      <c r="B27" s="32" t="s">
         <v>92</v>
       </c>
       <c r="C27" s="3" t="s">
@@ -4690,7 +4753,7 @@
       <c r="A28" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B28" s="2" t="s">
+      <c r="B28" s="32" t="s">
         <v>92</v>
       </c>
       <c r="C28" s="3" t="s">
@@ -4701,7 +4764,7 @@
       <c r="A29" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B29" s="2" t="s">
+      <c r="B29" s="32" t="s">
         <v>92</v>
       </c>
       <c r="C29" s="3" t="s">
@@ -4712,7 +4775,7 @@
       <c r="A30" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B30" s="2" t="s">
+      <c r="B30" s="32" t="s">
         <v>92</v>
       </c>
       <c r="C30" s="3" t="s">
@@ -4723,7 +4786,7 @@
       <c r="A31" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B31" s="2" t="s">
+      <c r="B31" s="32" t="s">
         <v>92</v>
       </c>
       <c r="C31" s="3" t="s">
@@ -4734,260 +4797,260 @@
       <c r="A32" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B32" s="2" t="s">
+      <c r="B32" s="32" t="s">
         <v>92</v>
       </c>
-      <c r="C32" s="24" t="s">
+      <c r="C32" s="32" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="33" spans="1:3" ht="16" x14ac:dyDescent="0.4">
-      <c r="A33" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B33" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>90</v>
+      <c r="A33" s="33" t="s">
+        <v>4</v>
+      </c>
+      <c r="B33" s="34" t="s">
+        <v>178</v>
+      </c>
+      <c r="C33" s="34" t="s">
+        <v>178</v>
       </c>
     </row>
     <row r="34" spans="1:3" ht="16" x14ac:dyDescent="0.4">
       <c r="A34" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B34" s="2" t="s">
+      <c r="B34" s="32" t="s">
         <v>87</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>166</v>
+        <v>90</v>
       </c>
     </row>
     <row r="35" spans="1:3" ht="16" x14ac:dyDescent="0.4">
       <c r="A35" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B35" s="2" t="s">
+      <c r="B35" s="32" t="s">
         <v>87</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>88</v>
+        <v>166</v>
       </c>
     </row>
     <row r="36" spans="1:3" ht="16" x14ac:dyDescent="0.4">
-      <c r="A36" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B36" s="2" t="s">
+      <c r="A36" s="33" t="s">
+        <v>4</v>
+      </c>
+      <c r="B36" s="34" t="s">
         <v>87</v>
       </c>
-      <c r="C36" s="3" t="s">
-        <v>91</v>
+      <c r="C36" s="35" t="s">
+        <v>282</v>
       </c>
     </row>
     <row r="37" spans="1:3" ht="16" x14ac:dyDescent="0.4">
       <c r="A37" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B37" s="2" t="s">
+      <c r="B37" s="32" t="s">
         <v>87</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="38" spans="1:3" ht="16" x14ac:dyDescent="0.4">
       <c r="A38" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B38" s="2" t="s">
+      <c r="B38" s="32" t="s">
         <v>87</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>136</v>
+        <v>91</v>
       </c>
     </row>
     <row r="39" spans="1:3" ht="16" x14ac:dyDescent="0.4">
       <c r="A39" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B39" s="2" t="s">
+      <c r="B39" s="32" t="s">
         <v>87</v>
       </c>
-      <c r="C39" s="24" t="s">
-        <v>79</v>
+      <c r="C39" s="3" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="40" spans="1:3" ht="16" x14ac:dyDescent="0.4">
       <c r="A40" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B40" s="2" t="s">
-        <v>106</v>
+      <c r="B40" s="32" t="s">
+        <v>87</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>167</v>
+        <v>136</v>
       </c>
     </row>
     <row r="41" spans="1:3" ht="16" x14ac:dyDescent="0.4">
       <c r="A41" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B41" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="C41" s="3" t="s">
-        <v>138</v>
+      <c r="B41" s="32" t="s">
+        <v>87</v>
+      </c>
+      <c r="C41" s="32" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="42" spans="1:3" ht="16" x14ac:dyDescent="0.4">
       <c r="A42" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B42" s="2" t="s">
+      <c r="B42" s="32" t="s">
         <v>106</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="43" spans="1:3" ht="16" x14ac:dyDescent="0.4">
       <c r="A43" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B43" s="2" t="s">
+      <c r="B43" s="32" t="s">
         <v>106</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>169</v>
+        <v>138</v>
       </c>
     </row>
     <row r="44" spans="1:3" ht="16" x14ac:dyDescent="0.4">
       <c r="A44" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B44" s="2" t="s">
+      <c r="B44" s="32" t="s">
         <v>106</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>139</v>
+        <v>168</v>
       </c>
     </row>
     <row r="45" spans="1:3" ht="16" x14ac:dyDescent="0.4">
       <c r="A45" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B45" s="2" t="s">
+      <c r="B45" s="32" t="s">
         <v>106</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>140</v>
+        <v>169</v>
       </c>
     </row>
     <row r="46" spans="1:3" ht="16" x14ac:dyDescent="0.4">
       <c r="A46" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B46" s="2" t="s">
+      <c r="B46" s="32" t="s">
         <v>106</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="47" spans="1:3" ht="16" x14ac:dyDescent="0.4">
       <c r="A47" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B47" s="2" t="s">
+      <c r="B47" s="32" t="s">
         <v>106</v>
       </c>
-      <c r="C47" s="24" t="s">
-        <v>79</v>
+      <c r="C47" s="3" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="48" spans="1:3" ht="16" x14ac:dyDescent="0.4">
-      <c r="A48" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B48" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="C48" s="3" t="s">
-        <v>170</v>
+      <c r="A48" s="33" t="s">
+        <v>4</v>
+      </c>
+      <c r="B48" s="34" t="s">
+        <v>106</v>
+      </c>
+      <c r="C48" s="35" t="s">
+        <v>283</v>
       </c>
     </row>
     <row r="49" spans="1:3" ht="16" x14ac:dyDescent="0.4">
       <c r="A49" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B49" s="2" t="s">
-        <v>111</v>
+      <c r="B49" s="32" t="s">
+        <v>106</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>171</v>
+        <v>141</v>
       </c>
     </row>
     <row r="50" spans="1:3" ht="16" x14ac:dyDescent="0.4">
       <c r="A50" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B50" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="C50" s="3" t="s">
-        <v>112</v>
+      <c r="B50" s="32" t="s">
+        <v>106</v>
+      </c>
+      <c r="C50" s="32" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="51" spans="1:3" ht="16" x14ac:dyDescent="0.4">
       <c r="A51" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B51" s="2" t="s">
+      <c r="B51" s="32" t="s">
         <v>111</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="52" spans="1:3" ht="16" x14ac:dyDescent="0.4">
       <c r="A52" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B52" s="2" t="s">
+      <c r="B52" s="32" t="s">
         <v>111</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>173</v>
+        <v>112</v>
       </c>
     </row>
     <row r="53" spans="1:3" ht="16" x14ac:dyDescent="0.4">
       <c r="A53" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B53" s="2" t="s">
+      <c r="B53" s="32" t="s">
         <v>111</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="54" spans="1:3" ht="16" x14ac:dyDescent="0.4">
       <c r="A54" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B54" s="2" t="s">
+      <c r="B54" s="32" t="s">
         <v>111</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="55" spans="1:3" ht="16" x14ac:dyDescent="0.4">
       <c r="A55" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B55" s="2" t="s">
+      <c r="B55" s="32" t="s">
         <v>111</v>
       </c>
       <c r="C55" s="3" t="s">
@@ -4998,7 +5061,7 @@
       <c r="A56" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B56" s="2" t="s">
+      <c r="B56" s="32" t="s">
         <v>111</v>
       </c>
       <c r="C56" s="3" t="s">
@@ -5009,352 +5072,462 @@
       <c r="A57" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B57" s="2" t="s">
+      <c r="B57" s="32" t="s">
         <v>111</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="58" spans="1:3" ht="16" x14ac:dyDescent="0.4">
       <c r="A58" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B58" s="2" t="s">
+      <c r="B58" s="32" t="s">
         <v>111</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="59" spans="1:3" ht="16" x14ac:dyDescent="0.4">
       <c r="A59" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B59" s="2" t="s">
+      <c r="B59" s="32" t="s">
         <v>111</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
     </row>
     <row r="60" spans="1:3" ht="16" x14ac:dyDescent="0.4">
       <c r="A60" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B60" s="2" t="s">
+      <c r="B60" s="32" t="s">
         <v>111</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
     <row r="61" spans="1:3" ht="16" x14ac:dyDescent="0.4">
       <c r="A61" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B61" s="2" t="s">
+      <c r="B61" s="32" t="s">
         <v>111</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
     </row>
     <row r="62" spans="1:3" ht="16" x14ac:dyDescent="0.4">
       <c r="A62" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B62" s="2" t="s">
+      <c r="B62" s="32" t="s">
         <v>111</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
     </row>
     <row r="63" spans="1:3" ht="16" x14ac:dyDescent="0.4">
       <c r="A63" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B63" s="2" t="s">
+      <c r="B63" s="32" t="s">
         <v>111</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
     </row>
     <row r="64" spans="1:3" ht="16" x14ac:dyDescent="0.4">
       <c r="A64" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B64" s="2" t="s">
+      <c r="B64" s="32" t="s">
         <v>111</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>185</v>
+        <v>152</v>
       </c>
     </row>
     <row r="65" spans="1:3" ht="16" x14ac:dyDescent="0.4">
       <c r="A65" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B65" s="2" t="s">
+      <c r="B65" s="32" t="s">
         <v>111</v>
       </c>
-      <c r="C65" s="3" t="s">
-        <v>186</v>
+      <c r="C65" s="32" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="66" spans="1:3" ht="16" x14ac:dyDescent="0.4">
-      <c r="A66" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B66" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="C66" s="3" t="s">
-        <v>150</v>
+      <c r="A66" s="33" t="s">
+        <v>4</v>
+      </c>
+      <c r="B66" s="34" t="s">
+        <v>284</v>
+      </c>
+      <c r="C66" s="34" t="s">
+        <v>284</v>
       </c>
     </row>
     <row r="67" spans="1:3" ht="16" x14ac:dyDescent="0.4">
-      <c r="A67" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B67" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="C67" s="3" t="s">
-        <v>152</v>
+      <c r="A67" s="33" t="s">
+        <v>4</v>
+      </c>
+      <c r="B67" s="34" t="s">
+        <v>266</v>
+      </c>
+      <c r="C67" s="34" t="s">
+        <v>170</v>
       </c>
     </row>
     <row r="68" spans="1:3" ht="16" x14ac:dyDescent="0.4">
-      <c r="A68" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B68" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="C68" s="24" t="s">
-        <v>79</v>
+      <c r="A68" s="33" t="s">
+        <v>4</v>
+      </c>
+      <c r="B68" s="34" t="s">
+        <v>266</v>
+      </c>
+      <c r="C68" s="34" t="s">
+        <v>172</v>
       </c>
     </row>
     <row r="69" spans="1:3" ht="16" x14ac:dyDescent="0.4">
-      <c r="A69" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="B69" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="C69" s="3" t="s">
-        <v>188</v>
+      <c r="A69" s="33" t="s">
+        <v>4</v>
+      </c>
+      <c r="B69" s="34" t="s">
+        <v>266</v>
+      </c>
+      <c r="C69" s="34" t="s">
+        <v>175</v>
       </c>
     </row>
     <row r="70" spans="1:3" ht="16" x14ac:dyDescent="0.4">
-      <c r="A70" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="B70" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="C70" s="3" t="s">
-        <v>190</v>
+      <c r="A70" s="33" t="s">
+        <v>4</v>
+      </c>
+      <c r="B70" s="34" t="s">
+        <v>266</v>
+      </c>
+      <c r="C70" s="34" t="s">
+        <v>181</v>
       </c>
     </row>
     <row r="71" spans="1:3" ht="16" x14ac:dyDescent="0.4">
-      <c r="A71" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="B71" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="C71" s="3" t="s">
-        <v>191</v>
+      <c r="A71" s="33" t="s">
+        <v>4</v>
+      </c>
+      <c r="B71" s="34" t="s">
+        <v>266</v>
+      </c>
+      <c r="C71" s="34" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="72" spans="1:3" ht="16" x14ac:dyDescent="0.4">
-      <c r="A72" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="B72" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="C72" s="3" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="73" spans="1:3" ht="32" x14ac:dyDescent="0.4">
-      <c r="A73" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="B73" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="C73" s="3" t="s">
-        <v>193</v>
+      <c r="A72" s="33" t="s">
+        <v>4</v>
+      </c>
+      <c r="B72" s="34" t="s">
+        <v>285</v>
+      </c>
+      <c r="C72" s="34" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" ht="16" x14ac:dyDescent="0.4">
+      <c r="A73" s="33" t="s">
+        <v>4</v>
+      </c>
+      <c r="B73" s="34" t="s">
+        <v>286</v>
+      </c>
+      <c r="C73" s="34" t="s">
+        <v>286</v>
       </c>
     </row>
     <row r="74" spans="1:3" ht="16" x14ac:dyDescent="0.4">
-      <c r="A74" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="B74" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="C74" s="2" t="s">
-        <v>194</v>
+      <c r="A74" s="33" t="s">
+        <v>4</v>
+      </c>
+      <c r="B74" s="34" t="s">
+        <v>149</v>
+      </c>
+      <c r="C74" s="34" t="s">
+        <v>149</v>
       </c>
     </row>
     <row r="75" spans="1:3" ht="16" x14ac:dyDescent="0.4">
       <c r="A75" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="B75" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="C75" s="2" t="s">
-        <v>79</v>
+      <c r="B75" s="32" t="s">
+        <v>187</v>
+      </c>
+      <c r="C75" s="3" t="s">
+        <v>188</v>
       </c>
     </row>
     <row r="76" spans="1:3" ht="16" x14ac:dyDescent="0.4">
       <c r="A76" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="B76" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="C76" s="2" t="s">
-        <v>195</v>
+        <v>153</v>
+      </c>
+      <c r="B76" s="32" t="s">
+        <v>189</v>
+      </c>
+      <c r="C76" s="3" t="s">
+        <v>190</v>
       </c>
     </row>
     <row r="77" spans="1:3" ht="16" x14ac:dyDescent="0.4">
       <c r="A77" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="B77" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="C77" s="2" t="s">
-        <v>196</v>
+        <v>153</v>
+      </c>
+      <c r="B77" s="32" t="s">
+        <v>189</v>
+      </c>
+      <c r="C77" s="3" t="s">
+        <v>191</v>
       </c>
     </row>
     <row r="78" spans="1:3" ht="16" x14ac:dyDescent="0.4">
       <c r="A78" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="B78" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="C78" s="2" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="79" spans="1:3" ht="16" x14ac:dyDescent="0.4">
+        <v>153</v>
+      </c>
+      <c r="B78" s="32" t="s">
+        <v>189</v>
+      </c>
+      <c r="C78" s="3" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" ht="32" x14ac:dyDescent="0.4">
       <c r="A79" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="B79" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="C79" s="2" t="s">
-        <v>198</v>
+        <v>153</v>
+      </c>
+      <c r="B79" s="32" t="s">
+        <v>189</v>
+      </c>
+      <c r="C79" s="3" t="s">
+        <v>193</v>
       </c>
     </row>
     <row r="80" spans="1:3" ht="16" x14ac:dyDescent="0.4">
       <c r="A80" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="B80" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="C80" s="2" t="s">
-        <v>79</v>
+        <v>153</v>
+      </c>
+      <c r="B80" s="32" t="s">
+        <v>194</v>
+      </c>
+      <c r="C80" s="32" t="s">
+        <v>194</v>
       </c>
     </row>
     <row r="81" spans="1:3" ht="16" x14ac:dyDescent="0.4">
       <c r="A81" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="B81" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="C81" s="2" t="s">
-        <v>200</v>
+        <v>153</v>
+      </c>
+      <c r="B81" s="32" t="s">
+        <v>79</v>
+      </c>
+      <c r="C81" s="32" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="82" spans="1:3" ht="16" x14ac:dyDescent="0.4">
       <c r="A82" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="B82" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="C82" s="2" t="s">
-        <v>79</v>
+        <v>154</v>
+      </c>
+      <c r="B82" s="32" t="s">
+        <v>195</v>
+      </c>
+      <c r="C82" s="32" t="s">
+        <v>195</v>
       </c>
     </row>
     <row r="83" spans="1:3" ht="16" x14ac:dyDescent="0.4">
       <c r="A83" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="B83" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="C83" s="2" t="s">
-        <v>201</v>
+        <v>154</v>
+      </c>
+      <c r="B83" s="32" t="s">
+        <v>196</v>
+      </c>
+      <c r="C83" s="32" t="s">
+        <v>196</v>
       </c>
     </row>
     <row r="84" spans="1:3" ht="16" x14ac:dyDescent="0.4">
       <c r="A84" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="B84" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="C84" s="2" t="s">
-        <v>202</v>
+        <v>154</v>
+      </c>
+      <c r="B84" s="32" t="s">
+        <v>197</v>
+      </c>
+      <c r="C84" s="32" t="s">
+        <v>197</v>
       </c>
     </row>
     <row r="85" spans="1:3" ht="16" x14ac:dyDescent="0.4">
       <c r="A85" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="B85" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="C85" s="2" t="s">
-        <v>203</v>
+        <v>154</v>
+      </c>
+      <c r="B85" s="32" t="s">
+        <v>198</v>
+      </c>
+      <c r="C85" s="32" t="s">
+        <v>198</v>
       </c>
     </row>
     <row r="86" spans="1:3" ht="16" x14ac:dyDescent="0.4">
-      <c r="A86" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="B86" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="C86" s="2" t="s">
-        <v>204</v>
+      <c r="A86" s="33" t="s">
+        <v>154</v>
+      </c>
+      <c r="B86" s="34" t="s">
+        <v>287</v>
+      </c>
+      <c r="C86" s="34" t="s">
+        <v>287</v>
       </c>
     </row>
     <row r="87" spans="1:3" ht="16" x14ac:dyDescent="0.4">
-      <c r="A87" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="B87" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="C87" s="2" t="s">
-        <v>205</v>
+      <c r="A87" s="33" t="s">
+        <v>154</v>
+      </c>
+      <c r="B87" s="34" t="s">
+        <v>288</v>
+      </c>
+      <c r="C87" s="34" t="s">
+        <v>288</v>
       </c>
     </row>
     <row r="88" spans="1:3" ht="16" x14ac:dyDescent="0.4">
       <c r="A88" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="B88" s="32" t="s">
+        <v>79</v>
+      </c>
+      <c r="C88" s="32" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" ht="16" x14ac:dyDescent="0.4">
+      <c r="A89" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="B89" s="32" t="s">
+        <v>200</v>
+      </c>
+      <c r="C89" s="32" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" ht="16" x14ac:dyDescent="0.4">
+      <c r="A90" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="B90" s="32" t="s">
+        <v>79</v>
+      </c>
+      <c r="C90" s="32" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" ht="16" x14ac:dyDescent="0.4">
+      <c r="A91" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="B88" s="24" t="s">
-        <v>79</v>
-      </c>
-      <c r="C88" s="24" t="s">
-        <v>79</v>
+      <c r="B91" s="32" t="s">
+        <v>63</v>
+      </c>
+      <c r="C91" s="32" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" ht="16" x14ac:dyDescent="0.4">
+      <c r="A92" s="33" t="s">
+        <v>85</v>
+      </c>
+      <c r="B92" s="34" t="s">
+        <v>63</v>
+      </c>
+      <c r="C92" s="34" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" ht="16" x14ac:dyDescent="0.4">
+      <c r="A93" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B93" s="32" t="s">
+        <v>63</v>
+      </c>
+      <c r="C93" s="32" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" ht="16" x14ac:dyDescent="0.4">
+      <c r="A94" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B94" s="32" t="s">
+        <v>76</v>
+      </c>
+      <c r="C94" s="32" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" ht="16" x14ac:dyDescent="0.4">
+      <c r="A95" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B95" s="32" t="s">
+        <v>76</v>
+      </c>
+      <c r="C95" s="32" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" ht="16" x14ac:dyDescent="0.4">
+      <c r="A96" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B96" s="32" t="s">
+        <v>76</v>
+      </c>
+      <c r="C96" s="32" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" ht="16" x14ac:dyDescent="0.4">
+      <c r="A97" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B97" s="32" t="s">
+        <v>79</v>
+      </c>
+      <c r="C97" s="32" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" ht="16" x14ac:dyDescent="0.4">
+      <c r="A98" s="36" t="s">
+        <v>290</v>
+      </c>
+      <c r="B98" s="37" t="s">
+        <v>290</v>
+      </c>
+      <c r="C98" s="37" t="s">
+        <v>290</v>
       </c>
     </row>
   </sheetData>

--- a/List_of_crops_update_all_3.xlsx
+++ b/List_of_crops_update_all_3.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GIT\antigravity\Land cover\github\Land-cover-validation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BAE4D40-CA25-4100-A52A-EF5E5FC49B12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8271ABA9-926C-42FF-BBEE-A318F16E8794}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19110" yWindow="0" windowWidth="19380" windowHeight="20970" activeTab="4" xr2:uid="{ADA269A6-2ED3-4A77-8230-6F13C182E555}"/>
+    <workbookView xWindow="38310" yWindow="0" windowWidth="19380" windowHeight="20970" activeTab="4" xr2:uid="{ADA269A6-2ED3-4A77-8230-6F13C182E555}"/>
   </bookViews>
   <sheets>
     <sheet name="Crop_list_HND" sheetId="8" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1524" uniqueCount="291">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1557" uniqueCount="300">
   <si>
     <t>Level_1</t>
   </si>
@@ -919,13 +919,40 @@
   </si>
   <si>
     <t>Vegetated Wetlands</t>
+  </si>
+  <si>
+    <t>Pasture</t>
+  </si>
+  <si>
+    <t>Nappier</t>
+  </si>
+  <si>
+    <t>Oat</t>
+  </si>
+  <si>
+    <t>Grass</t>
+  </si>
+  <si>
+    <t>Oil Crop</t>
+  </si>
+  <si>
+    <t>canolla</t>
+  </si>
+  <si>
+    <t>simsim</t>
+  </si>
+  <si>
+    <t>mixed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Other </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="28" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -938,11 +965,6 @@
       <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
-      <name val="Aptos"/>
     </font>
     <font>
       <sz val="11"/>
@@ -997,13 +1019,133 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF000000"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Aptos Display"/>
+      <family val="2"/>
+      <scheme val="major"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C5700"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="14">
+  <fills count="45">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1078,12 +1220,185 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="18">
     <border>
       <left/>
       <right/>
@@ -1188,78 +1503,240 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
-        <color indexed="64"/>
+        <color rgb="FF7F7F7F"/>
       </left>
       <right style="thin">
-        <color indexed="64"/>
+        <color rgb="FF7F7F7F"/>
       </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top/>
-      <bottom/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="18" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="19" borderId="16" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="27" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="27" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="27" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="27" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="27" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="27" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="13" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="44" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="42">
+    <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
+    <cellStyle name="20% - Accent2" xfId="23" builtinId="34" customBuiltin="1"/>
+    <cellStyle name="20% - Accent3" xfId="27" builtinId="38" customBuiltin="1"/>
+    <cellStyle name="20% - Accent4" xfId="31" builtinId="42" customBuiltin="1"/>
+    <cellStyle name="20% - Accent5" xfId="35" builtinId="46" customBuiltin="1"/>
+    <cellStyle name="20% - Accent6" xfId="39" builtinId="50" customBuiltin="1"/>
+    <cellStyle name="40% - Accent1" xfId="20" builtinId="31" customBuiltin="1"/>
+    <cellStyle name="40% - Accent2" xfId="24" builtinId="35" customBuiltin="1"/>
+    <cellStyle name="40% - Accent3" xfId="28" builtinId="39" customBuiltin="1"/>
+    <cellStyle name="40% - Accent4" xfId="32" builtinId="43" customBuiltin="1"/>
+    <cellStyle name="40% - Accent5" xfId="36" builtinId="47" customBuiltin="1"/>
+    <cellStyle name="40% - Accent6" xfId="40" builtinId="51" customBuiltin="1"/>
+    <cellStyle name="60% - Accent1" xfId="21" builtinId="32" customBuiltin="1"/>
+    <cellStyle name="60% - Accent2" xfId="25" builtinId="36" customBuiltin="1"/>
+    <cellStyle name="60% - Accent3" xfId="29" builtinId="40" customBuiltin="1"/>
+    <cellStyle name="60% - Accent4" xfId="33" builtinId="44" customBuiltin="1"/>
+    <cellStyle name="60% - Accent5" xfId="37" builtinId="48" customBuiltin="1"/>
+    <cellStyle name="60% - Accent6" xfId="41" builtinId="52" customBuiltin="1"/>
+    <cellStyle name="Accent1" xfId="18" builtinId="29" customBuiltin="1"/>
+    <cellStyle name="Accent2" xfId="22" builtinId="33" customBuiltin="1"/>
+    <cellStyle name="Accent3" xfId="26" builtinId="37" customBuiltin="1"/>
+    <cellStyle name="Accent4" xfId="30" builtinId="41" customBuiltin="1"/>
+    <cellStyle name="Accent5" xfId="34" builtinId="45" customBuiltin="1"/>
+    <cellStyle name="Accent6" xfId="38" builtinId="49" customBuiltin="1"/>
+    <cellStyle name="Bad" xfId="7" builtinId="27" customBuiltin="1"/>
+    <cellStyle name="Calculation" xfId="11" builtinId="22" customBuiltin="1"/>
+    <cellStyle name="Check Cell" xfId="13" builtinId="23" customBuiltin="1"/>
+    <cellStyle name="Explanatory Text" xfId="16" builtinId="53" customBuiltin="1"/>
+    <cellStyle name="Good" xfId="6" builtinId="26" customBuiltin="1"/>
+    <cellStyle name="Heading 1" xfId="2" builtinId="16" customBuiltin="1"/>
+    <cellStyle name="Heading 2" xfId="3" builtinId="17" customBuiltin="1"/>
+    <cellStyle name="Heading 3" xfId="4" builtinId="18" customBuiltin="1"/>
+    <cellStyle name="Heading 4" xfId="5" builtinId="19" customBuiltin="1"/>
+    <cellStyle name="Input" xfId="9" builtinId="20" customBuiltin="1"/>
+    <cellStyle name="Linked Cell" xfId="12" builtinId="24" customBuiltin="1"/>
+    <cellStyle name="Neutral" xfId="8" builtinId="28" customBuiltin="1"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Note" xfId="15" builtinId="10" customBuiltin="1"/>
+    <cellStyle name="Output" xfId="10" builtinId="21" customBuiltin="1"/>
+    <cellStyle name="Title" xfId="1" builtinId="15" customBuiltin="1"/>
+    <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
+    <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1592,868 +2069,868 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D7243B40-C8D7-464C-A7B9-7DE02DF4FE0D}">
   <dimension ref="A1:C78"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.453125" customWidth="1"/>
+    <col min="2" max="2" width="13.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A1" s="6" t="s">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="7" t="s">
+    <row r="2" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="B2" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="C2" s="9" t="s">
+      <c r="C2" s="7" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A3" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="8" t="s">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="C3" s="6" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A4" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" s="9" t="s">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="9" t="s">
+      <c r="C4" s="7" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A5" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5" s="8" t="s">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="9" t="s">
+      <c r="C5" s="7" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A6" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="B6" s="9" t="s">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C6" s="9" t="s">
+      <c r="C6" s="7" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A7" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="B7" s="8" t="s">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="C7" s="6" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A8" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="B8" s="9" t="s">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B8" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="9" t="s">
+      <c r="C8" s="7" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A9" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="B9" s="8" t="s">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B9" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="6" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A10" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="B10" s="9" t="s">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B10" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="9" t="s">
+      <c r="C10" s="7" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A11" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="B11" s="8" t="s">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B11" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="C11" s="8" t="s">
+      <c r="C11" s="6" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A12" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="B12" s="9" t="s">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B12" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="C12" s="9" t="s">
+      <c r="C12" s="7" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A13" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="B13" s="8" t="s">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B13" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C13" s="8" t="s">
+      <c r="C13" s="6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A14" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="B14" s="9" t="s">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B14" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="C14" s="9" t="s">
+      <c r="C14" s="7" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A15" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="B15" s="8" t="s">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A15" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B15" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C15" s="8" t="s">
+      <c r="C15" s="6" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A16" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="B16" s="9" t="s">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A16" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B16" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="C16" s="9" t="s">
+      <c r="C16" s="7" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A17" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="B17" s="8" t="s">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A17" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B17" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C17" s="8" t="s">
+      <c r="C17" s="6" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A18" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="B18" s="9" t="s">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A18" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B18" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="C18" s="9" t="s">
+      <c r="C18" s="7" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A19" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="B19" s="8" t="s">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A19" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B19" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="C19" s="8" t="s">
+      <c r="C19" s="6" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A20" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="B20" s="9" t="s">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A20" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B20" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="C20" s="9" t="s">
+      <c r="C20" s="7" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A21" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="B21" s="8" t="s">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A21" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B21" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="C21" s="8" t="s">
+      <c r="C21" s="6" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A22" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="B22" s="9" t="s">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A22" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B22" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="C22" s="9" t="s">
+      <c r="C22" s="7" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A23" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="B23" s="8" t="s">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A23" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B23" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="C23" s="8" t="s">
+      <c r="C23" s="6" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A24" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="B24" s="9" t="s">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A24" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B24" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="C24" s="9" t="s">
+      <c r="C24" s="7" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A25" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="B25" s="8" t="s">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A25" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B25" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="C25" s="8" t="s">
+      <c r="C25" s="6" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A26" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="B26" s="9" t="s">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A26" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B26" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="C26" s="9" t="s">
+      <c r="C26" s="7" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A27" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="B27" s="8" t="s">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A27" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B27" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="C27" s="8" t="s">
+      <c r="C27" s="6" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A28" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="B28" s="9" t="s">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A28" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B28" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="C28" s="9" t="s">
+      <c r="C28" s="7" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A29" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="B29" s="8" t="s">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A29" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B29" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="C29" s="8" t="s">
+      <c r="C29" s="6" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A30" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="B30" s="9" t="s">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A30" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B30" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="C30" s="9" t="s">
+      <c r="C30" s="7" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A31" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="B31" s="8" t="s">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A31" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B31" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="C31" s="8" t="s">
+      <c r="C31" s="6" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A32" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="B32" s="8" t="s">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A32" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B32" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="C32" s="10" t="s">
+      <c r="C32" s="8" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A33" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="B33" s="9" t="s">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A33" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B33" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="C33" s="9" t="s">
+      <c r="C33" s="7" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A34" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="B34" s="8" t="s">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A34" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B34" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="C34" s="8" t="s">
+      <c r="C34" s="6" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A35" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="B35" s="9" t="s">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A35" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B35" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="C35" s="9" t="s">
+      <c r="C35" s="7" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A36" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="B36" s="8" t="s">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A36" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B36" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="C36" s="8" t="s">
+      <c r="C36" s="6" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A37" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="B37" s="9" t="s">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A37" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B37" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="C37" s="9" t="s">
+      <c r="C37" s="7" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A38" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="B38" s="8" t="s">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A38" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B38" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="C38" s="8" t="s">
+      <c r="C38" s="6" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A39" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="B39" s="9" t="s">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A39" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B39" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="C39" s="9" t="s">
+      <c r="C39" s="7" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A40" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="B40" s="8" t="s">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A40" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B40" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="C40" s="8" t="s">
+      <c r="C40" s="6" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A41" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="B41" s="9" t="s">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A41" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B41" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="C41" s="9" t="s">
+      <c r="C41" s="7" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A42" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="B42" s="8" t="s">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A42" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B42" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="C42" s="8" t="s">
+      <c r="C42" s="6" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A43" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="B43" s="9" t="s">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A43" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B43" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="C43" s="9" t="s">
+      <c r="C43" s="7" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A44" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="B44" s="8" t="s">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A44" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B44" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="C44" s="8" t="s">
+      <c r="C44" s="6" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A45" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="B45" s="9" t="s">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A45" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B45" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="C45" s="9" t="s">
+      <c r="C45" s="7" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A46" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="B46" s="8" t="s">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A46" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B46" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="C46" s="8" t="s">
+      <c r="C46" s="6" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A47" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="B47" s="9" t="s">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A47" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B47" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="C47" s="9" t="s">
+      <c r="C47" s="7" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A48" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="B48" s="8" t="s">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A48" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B48" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="C48" s="8" t="s">
+      <c r="C48" s="6" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A49" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="B49" s="9" t="s">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A49" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B49" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="C49" s="9" t="s">
+      <c r="C49" s="7" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A50" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="B50" s="8" t="s">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A50" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B50" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="C50" s="8" t="s">
+      <c r="C50" s="6" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A51" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="B51" s="9" t="s">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A51" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B51" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="C51" s="9" t="s">
+      <c r="C51" s="7" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A52" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="B52" s="8" t="s">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A52" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B52" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="C52" s="8" t="s">
+      <c r="C52" s="6" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A53" s="9" t="s">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A53" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="B53" s="9" t="s">
+      <c r="B53" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="C53" s="9" t="s">
+      <c r="C53" s="7" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A54" s="9" t="s">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A54" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="B54" s="8" t="s">
+      <c r="B54" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="C54" s="8" t="s">
+      <c r="C54" s="6" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A55" s="9" t="s">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A55" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="B55" s="9" t="s">
+      <c r="B55" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="C55" s="9" t="s">
+      <c r="C55" s="7" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A56" s="9" t="s">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A56" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="B56" s="8" t="s">
+      <c r="B56" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="C56" s="8" t="s">
+      <c r="C56" s="6" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A57" s="9" t="s">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A57" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="B57" s="9" t="s">
+      <c r="B57" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="C57" s="9" t="s">
+      <c r="C57" s="7" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A58" s="9" t="s">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A58" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="B58" s="8" t="s">
+      <c r="B58" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="C58" s="8" t="s">
+      <c r="C58" s="6" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A59" s="9" t="s">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A59" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="B59" s="9" t="s">
+      <c r="B59" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="C59" s="9" t="s">
+      <c r="C59" s="7" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A60" s="9" t="s">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A60" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="B60" s="8" t="s">
+      <c r="B60" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="C60" s="8" t="s">
+      <c r="C60" s="6" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A61" s="9" t="s">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A61" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="B61" s="9" t="s">
+      <c r="B61" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="C61" s="9" t="s">
+      <c r="C61" s="7" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A62" s="9" t="s">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A62" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="B62" s="8" t="s">
+      <c r="B62" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="C62" s="8" t="s">
+      <c r="C62" s="6" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A63" s="9" t="s">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A63" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="B63" s="9" t="s">
+      <c r="B63" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="C63" s="9" t="s">
+      <c r="C63" s="7" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A64" s="9" t="s">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A64" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="B64" s="8" t="s">
+      <c r="B64" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="C64" s="8" t="s">
+      <c r="C64" s="6" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A65" s="9" t="s">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A65" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="B65" s="9" t="s">
+      <c r="B65" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="C65" s="9" t="s">
+      <c r="C65" s="7" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A66" s="9" t="s">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A66" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="B66" s="8" t="s">
+      <c r="B66" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="C66" s="8" t="s">
+      <c r="C66" s="6" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A67" s="9" t="s">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A67" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="B67" s="9" t="s">
+      <c r="B67" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="C67" s="9" t="s">
+      <c r="C67" s="7" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A68" s="9" t="s">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A68" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="B68" s="8" t="s">
+      <c r="B68" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="C68" s="8" t="s">
+      <c r="C68" s="6" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A69" s="9" t="s">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A69" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="B69" s="9" t="s">
+      <c r="B69" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="C69" s="9" t="s">
+      <c r="C69" s="7" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A70" s="8" t="s">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A70" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="B70" s="8" t="s">
+      <c r="B70" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="C70" s="8" t="s">
+      <c r="C70" s="6" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A71" s="9" t="s">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A71" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="B71" s="9" t="s">
+      <c r="B71" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="C71" s="9" t="s">
+      <c r="C71" s="7" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A72" s="8" t="s">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A72" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="B72" s="8" t="s">
+      <c r="B72" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="C72" s="8" t="s">
+      <c r="C72" s="6" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A73" s="9" t="s">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A73" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="B73" s="9" t="s">
+      <c r="B73" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="C73" s="9" t="s">
+      <c r="C73" s="7" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A74" s="8" t="s">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A74" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="B74" s="9" t="s">
+      <c r="B74" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="C74" s="9" t="s">
+      <c r="C74" s="7" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A75" s="9" t="s">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A75" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="B75" s="9" t="s">
+      <c r="B75" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="C75" s="9" t="s">
+      <c r="C75" s="7" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A76" s="8" t="s">
+    <row r="76" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A76" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="B76" s="9" t="s">
+      <c r="B76" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="C76" s="9" t="s">
+      <c r="C76" s="7" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A77" s="9" t="s">
+    <row r="77" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A77" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="B77" s="9" t="s">
+      <c r="B77" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="C77" s="9" t="s">
+      <c r="C77" s="7" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A78" s="8" t="s">
+    <row r="78" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A78" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="B78" s="9" t="s">
+      <c r="B78" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="C78" s="9" t="s">
+      <c r="C78" s="7" t="s">
         <v>40</v>
       </c>
     </row>
@@ -2465,868 +2942,868 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5E68490-0290-496A-96FF-4A55EF206F51}">
   <dimension ref="A1:C78"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.453125" customWidth="1"/>
+    <col min="2" max="2" width="13.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A1" s="6" t="s">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="7" t="s">
+    <row r="2" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="B2" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="C2" s="9" t="s">
+      <c r="C2" s="7" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A3" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="8" t="s">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="C3" s="6" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A4" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" s="9" t="s">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="9" t="s">
+      <c r="C4" s="7" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A5" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5" s="8" t="s">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="9" t="s">
+      <c r="C5" s="7" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A6" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="B6" s="9" t="s">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C6" s="9" t="s">
+      <c r="C6" s="7" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A7" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="B7" s="8" t="s">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="C7" s="6" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A8" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="B8" s="9" t="s">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B8" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="9" t="s">
+      <c r="C8" s="7" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A9" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="B9" s="8" t="s">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B9" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="6" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A10" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="B10" s="9" t="s">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B10" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="9" t="s">
+      <c r="C10" s="7" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A11" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="B11" s="8" t="s">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B11" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="C11" s="8" t="s">
+      <c r="C11" s="6" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A12" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="B12" s="9" t="s">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B12" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="C12" s="9" t="s">
+      <c r="C12" s="7" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A13" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="B13" s="8" t="s">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B13" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C13" s="8" t="s">
+      <c r="C13" s="6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A14" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="B14" s="9" t="s">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B14" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="C14" s="9" t="s">
+      <c r="C14" s="7" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A15" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="B15" s="8" t="s">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A15" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B15" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C15" s="8" t="s">
+      <c r="C15" s="6" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A16" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="B16" s="9" t="s">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A16" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B16" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="C16" s="9" t="s">
+      <c r="C16" s="7" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A17" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="B17" s="8" t="s">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A17" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B17" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C17" s="8" t="s">
+      <c r="C17" s="6" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A18" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="B18" s="9" t="s">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A18" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B18" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="C18" s="9" t="s">
+      <c r="C18" s="7" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A19" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="B19" s="8" t="s">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A19" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B19" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="C19" s="8" t="s">
+      <c r="C19" s="6" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A20" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="B20" s="9" t="s">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A20" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B20" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="C20" s="9" t="s">
+      <c r="C20" s="7" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A21" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="B21" s="8" t="s">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A21" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B21" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="C21" s="8" t="s">
+      <c r="C21" s="6" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A22" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="B22" s="9" t="s">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A22" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B22" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="C22" s="9" t="s">
+      <c r="C22" s="7" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A23" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="B23" s="8" t="s">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A23" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B23" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="C23" s="8" t="s">
+      <c r="C23" s="6" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A24" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="B24" s="9" t="s">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A24" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B24" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="C24" s="9" t="s">
+      <c r="C24" s="7" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A25" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="B25" s="8" t="s">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A25" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B25" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="C25" s="8" t="s">
+      <c r="C25" s="6" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A26" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="B26" s="9" t="s">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A26" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B26" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="C26" s="9" t="s">
+      <c r="C26" s="7" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A27" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="B27" s="8" t="s">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A27" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B27" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="C27" s="8" t="s">
+      <c r="C27" s="6" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A28" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="B28" s="9" t="s">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A28" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B28" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="C28" s="9" t="s">
+      <c r="C28" s="7" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A29" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="B29" s="8" t="s">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A29" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B29" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="C29" s="8" t="s">
+      <c r="C29" s="6" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A30" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="B30" s="9" t="s">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A30" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B30" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="C30" s="9" t="s">
+      <c r="C30" s="7" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A31" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="B31" s="8" t="s">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A31" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B31" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="C31" s="8" t="s">
+      <c r="C31" s="6" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A32" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="B32" s="8" t="s">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A32" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B32" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="C32" s="10" t="s">
+      <c r="C32" s="8" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A33" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="B33" s="9" t="s">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A33" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B33" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="C33" s="9" t="s">
+      <c r="C33" s="7" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A34" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="B34" s="8" t="s">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A34" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B34" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="C34" s="8" t="s">
+      <c r="C34" s="6" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A35" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="B35" s="9" t="s">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A35" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B35" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="C35" s="9" t="s">
+      <c r="C35" s="7" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A36" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="B36" s="8" t="s">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A36" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B36" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="C36" s="8" t="s">
+      <c r="C36" s="6" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A37" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="B37" s="9" t="s">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A37" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B37" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="C37" s="9" t="s">
+      <c r="C37" s="7" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A38" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="B38" s="8" t="s">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A38" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B38" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="C38" s="8" t="s">
+      <c r="C38" s="6" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A39" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="B39" s="9" t="s">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A39" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B39" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="C39" s="9" t="s">
+      <c r="C39" s="7" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A40" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="B40" s="8" t="s">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A40" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B40" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="C40" s="8" t="s">
+      <c r="C40" s="6" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A41" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="B41" s="9" t="s">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A41" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B41" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="C41" s="9" t="s">
+      <c r="C41" s="7" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A42" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="B42" s="8" t="s">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A42" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B42" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="C42" s="8" t="s">
+      <c r="C42" s="6" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A43" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="B43" s="9" t="s">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A43" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B43" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="C43" s="9" t="s">
+      <c r="C43" s="7" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A44" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="B44" s="8" t="s">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A44" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B44" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="C44" s="8" t="s">
+      <c r="C44" s="6" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A45" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="B45" s="9" t="s">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A45" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B45" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="C45" s="9" t="s">
+      <c r="C45" s="7" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A46" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="B46" s="8" t="s">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A46" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B46" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="C46" s="8" t="s">
+      <c r="C46" s="6" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A47" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="B47" s="9" t="s">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A47" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B47" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="C47" s="9" t="s">
+      <c r="C47" s="7" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A48" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="B48" s="8" t="s">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A48" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B48" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="C48" s="8" t="s">
+      <c r="C48" s="6" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A49" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="B49" s="9" t="s">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A49" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B49" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="C49" s="9" t="s">
+      <c r="C49" s="7" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A50" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="B50" s="8" t="s">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A50" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B50" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="C50" s="8" t="s">
+      <c r="C50" s="6" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A51" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="B51" s="9" t="s">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A51" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B51" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="C51" s="9" t="s">
+      <c r="C51" s="7" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A52" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="B52" s="8" t="s">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A52" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B52" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="C52" s="8" t="s">
+      <c r="C52" s="6" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A53" s="9" t="s">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A53" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="B53" s="9" t="s">
+      <c r="B53" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="C53" s="9" t="s">
+      <c r="C53" s="7" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A54" s="9" t="s">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A54" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="B54" s="8" t="s">
+      <c r="B54" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="C54" s="8" t="s">
+      <c r="C54" s="6" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A55" s="9" t="s">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A55" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="B55" s="9" t="s">
+      <c r="B55" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="C55" s="9" t="s">
+      <c r="C55" s="7" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A56" s="9" t="s">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A56" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="B56" s="8" t="s">
+      <c r="B56" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="C56" s="8" t="s">
+      <c r="C56" s="6" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A57" s="9" t="s">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A57" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="B57" s="9" t="s">
+      <c r="B57" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="C57" s="9" t="s">
+      <c r="C57" s="7" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A58" s="9" t="s">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A58" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="B58" s="8" t="s">
+      <c r="B58" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="C58" s="8" t="s">
+      <c r="C58" s="6" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A59" s="9" t="s">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A59" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="B59" s="9" t="s">
+      <c r="B59" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="C59" s="9" t="s">
+      <c r="C59" s="7" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A60" s="9" t="s">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A60" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="B60" s="8" t="s">
+      <c r="B60" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="C60" s="8" t="s">
+      <c r="C60" s="6" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A61" s="9" t="s">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A61" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="B61" s="9" t="s">
+      <c r="B61" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="C61" s="9" t="s">
+      <c r="C61" s="7" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A62" s="9" t="s">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A62" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="B62" s="8" t="s">
+      <c r="B62" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="C62" s="8" t="s">
+      <c r="C62" s="6" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A63" s="9" t="s">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A63" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="B63" s="9" t="s">
+      <c r="B63" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="C63" s="9" t="s">
+      <c r="C63" s="7" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A64" s="9" t="s">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A64" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="B64" s="8" t="s">
+      <c r="B64" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="C64" s="8" t="s">
+      <c r="C64" s="6" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A65" s="9" t="s">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A65" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="B65" s="9" t="s">
+      <c r="B65" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="C65" s="9" t="s">
+      <c r="C65" s="7" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A66" s="9" t="s">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A66" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="B66" s="8" t="s">
+      <c r="B66" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="C66" s="8" t="s">
+      <c r="C66" s="6" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A67" s="9" t="s">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A67" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="B67" s="9" t="s">
+      <c r="B67" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="C67" s="9" t="s">
+      <c r="C67" s="7" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A68" s="9" t="s">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A68" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="B68" s="8" t="s">
+      <c r="B68" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="C68" s="8" t="s">
+      <c r="C68" s="6" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A69" s="9" t="s">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A69" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="B69" s="9" t="s">
+      <c r="B69" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="C69" s="9" t="s">
+      <c r="C69" s="7" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A70" s="8" t="s">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A70" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="B70" s="8" t="s">
+      <c r="B70" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="C70" s="8" t="s">
+      <c r="C70" s="6" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A71" s="9" t="s">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A71" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="B71" s="9" t="s">
+      <c r="B71" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="C71" s="9" t="s">
+      <c r="C71" s="7" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A72" s="8" t="s">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A72" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="B72" s="8" t="s">
+      <c r="B72" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="C72" s="8" t="s">
+      <c r="C72" s="6" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A73" s="9" t="s">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A73" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="B73" s="9" t="s">
+      <c r="B73" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="C73" s="9" t="s">
+      <c r="C73" s="7" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A74" s="8" t="s">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A74" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="B74" s="9" t="s">
+      <c r="B74" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="C74" s="9" t="s">
+      <c r="C74" s="7" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A75" s="9" t="s">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A75" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="B75" s="9" t="s">
+      <c r="B75" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="C75" s="9" t="s">
+      <c r="C75" s="7" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A76" s="8" t="s">
+    <row r="76" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A76" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="B76" s="9" t="s">
+      <c r="B76" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="C76" s="9" t="s">
+      <c r="C76" s="7" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A77" s="9" t="s">
+    <row r="77" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A77" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="B77" s="9" t="s">
+      <c r="B77" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="C77" s="9" t="s">
+      <c r="C77" s="7" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A78" s="8" t="s">
+    <row r="78" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A78" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="B78" s="9" t="s">
+      <c r="B78" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="C78" s="9" t="s">
+      <c r="C78" s="7" t="s">
         <v>40</v>
       </c>
     </row>
@@ -3338,471 +3815,471 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53DA3773-6B5A-41DB-AD2A-A19E56B0A893}">
   <dimension ref="A1:C42"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="15.7265625" customWidth="1"/>
-    <col min="3" max="3" width="16.1796875" customWidth="1"/>
+    <col min="1" max="2" width="15.77734375" customWidth="1"/>
+    <col min="3" max="3" width="16.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A1" s="29" t="s">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="27" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="30" t="s">
+      <c r="B1" s="28" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="30" t="s">
+      <c r="C1" s="28" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A2" s="11" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" s="12" t="s">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="C2" s="12" t="s">
+      <c r="C2" s="10" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A3" s="11" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="13" t="s">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="11" t="s">
         <v>87</v>
       </c>
-      <c r="C3" s="13" t="s">
+      <c r="C3" s="11" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A4" s="11" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" s="12" t="s">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="C4" s="12" t="s">
+      <c r="C4" s="10" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A5" s="11" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5" s="13" t="s">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="11" t="s">
         <v>87</v>
       </c>
-      <c r="C5" s="13" t="s">
+      <c r="C5" s="11" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A6" s="11" t="s">
-        <v>4</v>
-      </c>
-      <c r="B6" s="12" t="s">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="C6" s="12" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A7" s="11" t="s">
-        <v>4</v>
-      </c>
-      <c r="B7" s="13" t="s">
+      <c r="C6" s="10" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="C7" s="13" t="s">
+      <c r="C7" s="11" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A8" s="11" t="s">
-        <v>4</v>
-      </c>
-      <c r="B8" s="12" t="s">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="B8" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="C8" s="12" t="s">
+      <c r="C8" s="10" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A9" s="11" t="s">
-        <v>4</v>
-      </c>
-      <c r="B9" s="13" t="s">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="B9" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="C9" s="13" t="s">
+      <c r="C9" s="11" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A10" s="11" t="s">
-        <v>4</v>
-      </c>
-      <c r="B10" s="12" t="s">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="B10" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="C10" s="12" t="s">
+      <c r="C10" s="10" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A11" s="11" t="s">
-        <v>4</v>
-      </c>
-      <c r="B11" s="13" t="s">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="B11" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="C11" s="13" t="s">
+      <c r="C11" s="11" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A12" s="11" t="s">
-        <v>4</v>
-      </c>
-      <c r="B12" s="12" t="s">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="B12" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="C12" s="12" t="s">
+      <c r="C12" s="10" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A13" s="11" t="s">
-        <v>4</v>
-      </c>
-      <c r="B13" s="13" t="s">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="B13" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="C13" s="13" t="s">
+      <c r="C13" s="11" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A14" s="11" t="s">
-        <v>4</v>
-      </c>
-      <c r="B14" s="12" t="s">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="B14" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="C14" s="12" t="s">
+      <c r="C14" s="10" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A15" s="11" t="s">
-        <v>4</v>
-      </c>
-      <c r="B15" s="13" t="s">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A15" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="B15" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="C15" s="13" t="s">
+      <c r="C15" s="11" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A16" s="11" t="s">
-        <v>4</v>
-      </c>
-      <c r="B16" s="12" t="s">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A16" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="B16" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="C16" s="12" t="s">
+      <c r="C16" s="10" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A17" s="11" t="s">
-        <v>4</v>
-      </c>
-      <c r="B17" s="13" t="s">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A17" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="B17" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="C17" s="13" t="s">
+      <c r="C17" s="11" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A18" s="11" t="s">
-        <v>4</v>
-      </c>
-      <c r="B18" s="12" t="s">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A18" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="B18" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="C18" s="12" t="s">
+      <c r="C18" s="10" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A19" s="11" t="s">
-        <v>4</v>
-      </c>
-      <c r="B19" s="13" t="s">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A19" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="B19" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="C19" s="13" t="s">
+      <c r="C19" s="11" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A20" s="11" t="s">
-        <v>4</v>
-      </c>
-      <c r="B20" s="12" t="s">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A20" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="B20" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="C20" s="12" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A21" s="11" t="s">
-        <v>4</v>
-      </c>
-      <c r="B21" s="13" t="s">
+      <c r="C20" s="10" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A21" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="B21" s="11" t="s">
         <v>106</v>
       </c>
-      <c r="C21" s="13" t="s">
+      <c r="C21" s="11" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A22" s="11" t="s">
-        <v>4</v>
-      </c>
-      <c r="B22" s="12" t="s">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A22" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="B22" s="10" t="s">
         <v>106</v>
       </c>
-      <c r="C22" s="12" t="s">
+      <c r="C22" s="10" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A23" s="11" t="s">
-        <v>4</v>
-      </c>
-      <c r="B23" s="13" t="s">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A23" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="B23" s="11" t="s">
         <v>106</v>
       </c>
-      <c r="C23" s="13" t="s">
+      <c r="C23" s="11" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A24" s="11" t="s">
-        <v>4</v>
-      </c>
-      <c r="B24" s="12" t="s">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A24" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="B24" s="10" t="s">
         <v>106</v>
       </c>
-      <c r="C24" s="12" t="s">
+      <c r="C24" s="10" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A25" s="11" t="s">
-        <v>4</v>
-      </c>
-      <c r="B25" s="13" t="s">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A25" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="B25" s="11" t="s">
         <v>106</v>
       </c>
-      <c r="C25" s="13" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A26" s="11" t="s">
-        <v>4</v>
-      </c>
-      <c r="B26" s="12" t="s">
+      <c r="C25" s="11" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A26" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="B26" s="10" t="s">
         <v>111</v>
       </c>
-      <c r="C26" s="12" t="s">
+      <c r="C26" s="10" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A27" s="11" t="s">
-        <v>4</v>
-      </c>
-      <c r="B27" s="13" t="s">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A27" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="B27" s="11" t="s">
         <v>111</v>
       </c>
-      <c r="C27" s="13" t="s">
+      <c r="C27" s="11" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A28" s="11" t="s">
-        <v>4</v>
-      </c>
-      <c r="B28" s="12" t="s">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A28" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="B28" s="10" t="s">
         <v>111</v>
       </c>
-      <c r="C28" s="12" t="s">
+      <c r="C28" s="10" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A29" s="11" t="s">
-        <v>4</v>
-      </c>
-      <c r="B29" s="13" t="s">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A29" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="B29" s="11" t="s">
         <v>111</v>
       </c>
-      <c r="C29" s="13" t="s">
+      <c r="C29" s="11" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A30" s="11" t="s">
-        <v>4</v>
-      </c>
-      <c r="B30" s="12" t="s">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A30" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="B30" s="10" t="s">
         <v>111</v>
       </c>
-      <c r="C30" s="12" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A31" s="11" t="s">
-        <v>4</v>
-      </c>
-      <c r="B31" s="13" t="s">
+      <c r="C30" s="10" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A31" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="B31" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="C31" s="13" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A32" s="14" t="s">
+      <c r="C31" s="11" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A32" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="B32" s="12" t="s">
-        <v>79</v>
-      </c>
-      <c r="C32" s="12" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A33" s="15" t="s">
+      <c r="B32" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="C32" s="10" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A33" s="13" t="s">
         <v>116</v>
       </c>
-      <c r="B33" s="13" t="s">
+      <c r="B33" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="C33" s="13" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A34" s="15" t="s">
+      <c r="C33" s="11" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A34" s="13" t="s">
         <v>116</v>
       </c>
-      <c r="B34" s="12" t="s">
+      <c r="B34" s="10" t="s">
         <v>117</v>
       </c>
-      <c r="C34" s="12" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A35" s="15" t="s">
+      <c r="C34" s="10" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A35" s="13" t="s">
         <v>116</v>
       </c>
-      <c r="B35" s="13" t="s">
-        <v>79</v>
-      </c>
-      <c r="C35" s="13" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A36" s="16" t="s">
+      <c r="B35" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="C35" s="11" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A36" s="14" t="s">
         <v>118</v>
       </c>
-      <c r="B36" s="12" t="s">
-        <v>79</v>
-      </c>
-      <c r="C36" s="12" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A37" s="17" t="s">
+      <c r="B36" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="C36" s="10" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A37" s="15" t="s">
         <v>84</v>
       </c>
-      <c r="B37" s="13" t="s">
-        <v>79</v>
-      </c>
-      <c r="C37" s="13" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A38" s="18" t="s">
+      <c r="B37" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="C37" s="11" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A38" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="B38" s="12" t="s">
-        <v>79</v>
-      </c>
-      <c r="C38" s="12" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A39" s="19" t="s">
+      <c r="B38" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="C38" s="10" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A39" s="17" t="s">
         <v>85</v>
       </c>
-      <c r="B39" s="13" t="s">
-        <v>79</v>
-      </c>
-      <c r="C39" s="13" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A40" s="20" t="s">
+      <c r="B39" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="C39" s="11" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A40" s="18" t="s">
         <v>80</v>
       </c>
-      <c r="B40" s="12" t="s">
-        <v>79</v>
-      </c>
-      <c r="C40" s="12" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A41" s="21" t="s">
+      <c r="B40" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="C40" s="10" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A41" s="19" t="s">
         <v>86</v>
       </c>
-      <c r="B41" s="13" t="s">
-        <v>79</v>
-      </c>
-      <c r="C41" s="13" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A42" s="22" t="s">
-        <v>79</v>
-      </c>
-      <c r="B42" s="22" t="s">
-        <v>79</v>
-      </c>
-      <c r="C42" s="22" t="s">
+      <c r="B41" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="C41" s="11" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A42" s="20" t="s">
+        <v>79</v>
+      </c>
+      <c r="B42" s="20" t="s">
+        <v>79</v>
+      </c>
+      <c r="C42" s="20" t="s">
         <v>79</v>
       </c>
     </row>
@@ -3814,626 +4291,626 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{528A2A70-2F6F-40BB-B5B3-D09006214570}">
   <dimension ref="A1:C56"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="20.1796875" customWidth="1"/>
-    <col min="2" max="2" width="16.54296875" customWidth="1"/>
-    <col min="3" max="3" width="22.81640625" customWidth="1"/>
+    <col min="1" max="1" width="20.21875" customWidth="1"/>
+    <col min="2" max="2" width="16.5546875" customWidth="1"/>
+    <col min="3" max="3" width="22.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A1" s="29" t="s">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="27" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="30" t="s">
+      <c r="B1" s="28" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="30" t="s">
+      <c r="C1" s="28" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A2" s="4" t="s">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="1" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A3" s="4" t="s">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="1" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A4" s="4" t="s">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="2" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A5" s="4" t="s">
+      <c r="C4" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="1" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A6" s="4" t="s">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="1" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A7" s="4" t="s">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" s="1" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A8" s="4" t="s">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="C8" s="2" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A9" s="4" t="s">
+      <c r="C8" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="B9" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A10" s="4" t="s">
+      <c r="B9" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="C10" s="3" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A11" s="4" t="s">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="C11" s="1" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A12" s="4" t="s">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="C12" s="3" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A13" s="4" t="s">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B13" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="C13" s="1" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A14" s="4" t="s">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="B14" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="C14" s="2" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A15" s="4" t="s">
+      <c r="C14" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A15" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="B15" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A16" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B16" s="2" t="s">
+      <c r="B15" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A16" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B16" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="C16" s="5" t="s">
+      <c r="C16" s="3" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A17" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B17" s="2" t="s">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A17" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B17" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="C17" s="5" t="s">
+      <c r="C17" s="3" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A18" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B18" s="2" t="s">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A18" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B18" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="C18" s="5" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A19" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B19" s="2" t="s">
+      <c r="C18" s="3" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A19" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B19" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="C19" s="5" t="s">
+      <c r="C19" s="3" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A20" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B20" s="2" t="s">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A20" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B20" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="C20" s="5" t="s">
+      <c r="C20" s="3" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="29" x14ac:dyDescent="0.35">
-      <c r="A21" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B21" s="2" t="s">
+    <row r="21" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A21" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B21" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="C21" s="5" t="s">
+      <c r="C21" s="3" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A22" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B22" s="2" t="s">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A22" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B22" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="C22" s="5" t="s">
+      <c r="C22" s="3" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A23" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B23" s="2" t="s">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A23" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B23" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="C23" s="5" t="s">
+      <c r="C23" s="3" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A24" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B24" s="2" t="s">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A24" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B24" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="C24" s="5" t="s">
+      <c r="C24" s="3" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A25" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B25" s="2" t="s">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A25" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B25" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="C25" s="5" t="s">
+      <c r="C25" s="3" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A26" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B26" s="2" t="s">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A26" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B26" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="C26" s="5" t="s">
+      <c r="C26" s="3" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A27" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B27" s="2" t="s">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A27" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B27" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="C27" s="5" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A28" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B28" s="2" t="s">
+      <c r="C27" s="3" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A28" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B28" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="C28" s="5" t="s">
+      <c r="C28" s="3" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A29" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B29" s="2" t="s">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A29" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B29" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="C29" s="5" t="s">
+      <c r="C29" s="3" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A30" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B30" s="2" t="s">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A30" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B30" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="C30" s="5" t="s">
+      <c r="C30" s="3" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A31" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B31" s="2" t="s">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A31" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B31" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="C31" s="5" t="s">
+      <c r="C31" s="3" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A32" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B32" s="2" t="s">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A32" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B32" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="C32" s="5" t="s">
+      <c r="C32" s="3" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A33" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B33" s="2" t="s">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A33" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B33" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="C33" s="5" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A34" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B34" s="2" t="s">
+      <c r="C33" s="3" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A34" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B34" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="C34" s="5" t="s">
+      <c r="C34" s="3" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A35" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B35" s="2" t="s">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A35" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B35" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="C35" s="5" t="s">
+      <c r="C35" s="3" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A36" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B36" s="2" t="s">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A36" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B36" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="C36" s="5" t="s">
+      <c r="C36" s="3" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A37" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B37" s="2" t="s">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A37" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B37" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="C37" s="5" t="s">
+      <c r="C37" s="3" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A38" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B38" s="2" t="s">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A38" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B38" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="C38" s="5" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A39" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B39" s="2" t="s">
+      <c r="C38" s="3" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A39" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B39" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="C39" s="5" t="s">
+      <c r="C39" s="3" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A40" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B40" s="2" t="s">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A40" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B40" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="C40" s="5" t="s">
+      <c r="C40" s="3" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A41" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B41" s="2" t="s">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A41" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B41" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="C41" s="5" t="s">
+      <c r="C41" s="3" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A42" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B42" s="2" t="s">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A42" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B42" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="C42" s="5" t="s">
+      <c r="C42" s="3" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A43" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B43" s="2" t="s">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A43" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B43" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="C43" s="5" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A44" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B44" s="2" t="s">
+      <c r="C43" s="3" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A44" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B44" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="C44" s="5" t="s">
+      <c r="C44" s="3" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A45" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B45" s="2" t="s">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A45" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B45" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="C45" s="5" t="s">
+      <c r="C45" s="3" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A46" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B46" s="2" t="s">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A46" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B46" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="C46" s="5" t="s">
+      <c r="C46" s="3" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A47" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B47" s="2" t="s">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A47" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B47" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="C47" s="5" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A48" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B48" s="2" t="s">
+      <c r="C47" s="3" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A48" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B48" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="C48" s="5" t="s">
+      <c r="C48" s="3" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A49" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B49" s="2" t="s">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A49" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B49" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="C49" s="5" t="s">
+      <c r="C49" s="3" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A50" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B50" s="2" t="s">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A50" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B50" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="C50" s="5" t="s">
+      <c r="C50" s="3" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A51" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B51" s="2" t="s">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A51" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B51" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="C51" s="5" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A52" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B52" s="2" t="s">
+      <c r="C51" s="3" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A52" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B52" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C52" s="5" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A53" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B53" s="31" t="s">
-        <v>79</v>
-      </c>
-      <c r="C53" s="5" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A54" s="4" t="s">
+      <c r="C52" s="3" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A53" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B53" s="29" t="s">
+        <v>79</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A54" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="B54" s="5" t="s">
+      <c r="B54" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="C54" s="5" t="s">
+      <c r="C54" s="3" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A55" s="4" t="s">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A55" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="B55" s="5" t="s">
+      <c r="B55" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="C55" s="5" t="s">
+      <c r="C55" s="3" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A56" s="4" t="s">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A56" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="B56" s="5" t="s">
+      <c r="B56" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="C56" s="5" t="s">
+      <c r="C56" s="3" t="s">
         <v>85</v>
       </c>
     </row>
@@ -4444,1089 +4921,1210 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F421573-7F45-40AE-9E4F-984A0D6DDEFC}">
-  <dimension ref="A1:C98"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:C109"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="33.26953125" customWidth="1"/>
-    <col min="2" max="2" width="22.453125" customWidth="1"/>
-    <col min="3" max="3" width="48.54296875" customWidth="1"/>
+    <col min="1" max="1" width="33.21875" customWidth="1"/>
+    <col min="2" max="2" width="22.44140625" customWidth="1"/>
+    <col min="3" max="3" width="48.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A1" s="29" t="s">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="27" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="30" t="s">
+      <c r="B1" s="28" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="30" t="s">
+      <c r="C1" s="28" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="16" x14ac:dyDescent="0.4">
-      <c r="A2" s="1" t="s">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" s="30" t="s">
         <v>116</v>
       </c>
-      <c r="B2" s="32" t="s">
+      <c r="B2" s="30" t="s">
         <v>63</v>
       </c>
-      <c r="C2" s="32" t="s">
+      <c r="C2" s="30" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="16" x14ac:dyDescent="0.4">
-      <c r="A3" s="1" t="s">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" s="30" t="s">
         <v>116</v>
       </c>
-      <c r="B3" s="32" t="s">
+      <c r="B3" s="30" t="s">
         <v>63</v>
       </c>
-      <c r="C3" s="32" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="16" x14ac:dyDescent="0.4">
-      <c r="A4" s="1" t="s">
+      <c r="C3" s="30" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" s="30" t="s">
         <v>116</v>
       </c>
-      <c r="B4" s="32" t="s">
+      <c r="B4" s="30" t="s">
         <v>120</v>
       </c>
-      <c r="C4" s="32" t="s">
+      <c r="C4" s="30" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="16" x14ac:dyDescent="0.4">
-      <c r="A5" s="1" t="s">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" s="30" t="s">
         <v>116</v>
       </c>
-      <c r="B5" s="32" t="s">
+      <c r="B5" s="30" t="s">
         <v>120</v>
       </c>
-      <c r="C5" s="32" t="s">
+      <c r="C5" s="30" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="16" x14ac:dyDescent="0.4">
-      <c r="A6" s="1" t="s">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" s="30" t="s">
         <v>116</v>
       </c>
-      <c r="B6" s="32" t="s">
+      <c r="B6" s="30" t="s">
         <v>120</v>
       </c>
-      <c r="C6" s="32" t="s">
+      <c r="C6" s="30" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="16" x14ac:dyDescent="0.4">
-      <c r="A7" s="1" t="s">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" s="30" t="s">
         <v>116</v>
       </c>
-      <c r="B7" s="32" t="s">
+      <c r="B7" s="30" t="s">
         <v>120</v>
       </c>
-      <c r="C7" s="32" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="16" x14ac:dyDescent="0.4">
-      <c r="A8" s="1" t="s">
+      <c r="C7" s="30" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" s="30" t="s">
         <v>116</v>
       </c>
-      <c r="B8" s="32" t="s">
-        <v>79</v>
-      </c>
-      <c r="C8" s="32" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" ht="16" x14ac:dyDescent="0.4">
-      <c r="A9" s="1" t="s">
+      <c r="B8" s="30" t="s">
+        <v>79</v>
+      </c>
+      <c r="C8" s="30" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" s="30" t="s">
         <v>84</v>
       </c>
-      <c r="B9" s="32" t="s">
+      <c r="B9" s="30" t="s">
         <v>157</v>
       </c>
-      <c r="C9" s="32" t="s">
+      <c r="C9" s="30" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="16" x14ac:dyDescent="0.4">
-      <c r="A10" s="1" t="s">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" s="30" t="s">
         <v>84</v>
       </c>
-      <c r="B10" s="32" t="s">
+      <c r="B10" s="30" t="s">
         <v>157</v>
       </c>
-      <c r="C10" s="32" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" ht="16" x14ac:dyDescent="0.4">
-      <c r="A11" s="1" t="s">
+      <c r="C10" s="30" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" s="30" t="s">
         <v>84</v>
       </c>
-      <c r="B11" s="32" t="s">
+      <c r="B11" s="30" t="s">
         <v>158</v>
       </c>
-      <c r="C11" s="32" t="s">
+      <c r="C11" s="30" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="16" x14ac:dyDescent="0.4">
-      <c r="A12" s="1" t="s">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" s="30" t="s">
         <v>84</v>
       </c>
-      <c r="B12" s="32" t="s">
+      <c r="B12" s="30" t="s">
         <v>158</v>
       </c>
-      <c r="C12" s="32" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" ht="16" x14ac:dyDescent="0.4">
-      <c r="A13" s="1" t="s">
+      <c r="C12" s="30" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13" s="30" t="s">
         <v>84</v>
       </c>
-      <c r="B13" s="32" t="s">
-        <v>79</v>
-      </c>
-      <c r="C13" s="32" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" ht="16" x14ac:dyDescent="0.4">
-      <c r="A14" s="1" t="s">
+      <c r="B13" s="30" t="s">
+        <v>79</v>
+      </c>
+      <c r="C13" s="30" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14" s="30" t="s">
         <v>75</v>
       </c>
-      <c r="B14" s="32" t="s">
+      <c r="B14" s="30" t="s">
         <v>159</v>
       </c>
-      <c r="C14" s="32" t="s">
+      <c r="C14" s="30" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="16" x14ac:dyDescent="0.4">
-      <c r="A15" s="1" t="s">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A15" s="30" t="s">
         <v>75</v>
       </c>
-      <c r="B15" s="32" t="s">
+      <c r="B15" s="30" t="s">
         <v>124</v>
       </c>
-      <c r="C15" s="32" t="s">
+      <c r="C15" s="30" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="16" x14ac:dyDescent="0.4">
-      <c r="A16" s="1" t="s">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A16" s="30" t="s">
         <v>75</v>
       </c>
-      <c r="B16" s="32" t="s">
+      <c r="B16" s="30" t="s">
         <v>125</v>
       </c>
-      <c r="C16" s="32" t="s">
+      <c r="C16" s="30" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="16" x14ac:dyDescent="0.4">
-      <c r="A17" s="1" t="s">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A17" s="30" t="s">
         <v>75</v>
       </c>
-      <c r="B17" s="32" t="s">
-        <v>79</v>
-      </c>
-      <c r="C17" s="32" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" ht="16" x14ac:dyDescent="0.4">
-      <c r="A18" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B18" s="32" t="s">
+      <c r="B17" s="30" t="s">
+        <v>79</v>
+      </c>
+      <c r="C17" s="30" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A18" s="30" t="s">
+        <v>4</v>
+      </c>
+      <c r="B18" s="30" t="s">
         <v>92</v>
       </c>
-      <c r="C18" s="3" t="s">
+      <c r="C18" s="30" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="16" x14ac:dyDescent="0.4">
-      <c r="A19" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B19" s="32" t="s">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A19" s="30" t="s">
+        <v>4</v>
+      </c>
+      <c r="B19" s="30" t="s">
         <v>92</v>
       </c>
-      <c r="C19" s="3" t="s">
+      <c r="C19" s="30" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="16" x14ac:dyDescent="0.4">
-      <c r="A20" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B20" s="32" t="s">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A20" s="30" t="s">
+        <v>4</v>
+      </c>
+      <c r="B20" s="30" t="s">
         <v>92</v>
       </c>
-      <c r="C20" s="3" t="s">
+      <c r="C20" s="30" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="16" x14ac:dyDescent="0.4">
-      <c r="A21" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B21" s="32" t="s">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A21" s="30" t="s">
+        <v>4</v>
+      </c>
+      <c r="B21" s="30" t="s">
         <v>92</v>
       </c>
-      <c r="C21" s="3" t="s">
+      <c r="C21" s="30" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="16" x14ac:dyDescent="0.4">
-      <c r="A22" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B22" s="32" t="s">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A22" s="30" t="s">
+        <v>4</v>
+      </c>
+      <c r="B22" s="30" t="s">
         <v>92</v>
       </c>
-      <c r="C22" s="3" t="s">
+      <c r="C22" s="30" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="16" x14ac:dyDescent="0.4">
-      <c r="A23" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B23" s="32" t="s">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A23" s="30" t="s">
+        <v>4</v>
+      </c>
+      <c r="B23" s="30" t="s">
         <v>92</v>
       </c>
-      <c r="C23" s="3" t="s">
+      <c r="C23" s="30" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="16" x14ac:dyDescent="0.4">
-      <c r="A24" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B24" s="32" t="s">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A24" s="30" t="s">
+        <v>4</v>
+      </c>
+      <c r="B24" s="30" t="s">
         <v>92</v>
       </c>
-      <c r="C24" s="3" t="s">
+      <c r="C24" s="30" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="16" x14ac:dyDescent="0.4">
-      <c r="A25" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B25" s="32" t="s">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A25" s="30" t="s">
+        <v>4</v>
+      </c>
+      <c r="B25" s="30" t="s">
         <v>92</v>
       </c>
-      <c r="C25" s="3" t="s">
+      <c r="C25" s="30" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="16" x14ac:dyDescent="0.4">
-      <c r="A26" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B26" s="32" t="s">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A26" s="30" t="s">
+        <v>4</v>
+      </c>
+      <c r="B26" s="30" t="s">
         <v>92</v>
       </c>
-      <c r="C26" s="3" t="s">
+      <c r="C26" s="30" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="27" spans="1:3" ht="16" x14ac:dyDescent="0.4">
-      <c r="A27" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B27" s="32" t="s">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A27" s="30" t="s">
+        <v>4</v>
+      </c>
+      <c r="B27" s="30" t="s">
         <v>92</v>
       </c>
-      <c r="C27" s="3" t="s">
+      <c r="C27" s="30" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="28" spans="1:3" ht="16" x14ac:dyDescent="0.4">
-      <c r="A28" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B28" s="32" t="s">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A28" s="30" t="s">
+        <v>4</v>
+      </c>
+      <c r="B28" s="30" t="s">
         <v>92</v>
       </c>
-      <c r="C28" s="3" t="s">
+      <c r="C28" s="30" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="29" spans="1:3" ht="16" x14ac:dyDescent="0.4">
-      <c r="A29" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B29" s="32" t="s">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A29" s="30" t="s">
+        <v>4</v>
+      </c>
+      <c r="B29" s="30" t="s">
         <v>92</v>
       </c>
-      <c r="C29" s="3" t="s">
+      <c r="C29" s="30" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="30" spans="1:3" ht="16" x14ac:dyDescent="0.4">
-      <c r="A30" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B30" s="32" t="s">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A30" s="30" t="s">
+        <v>4</v>
+      </c>
+      <c r="B30" s="30" t="s">
         <v>92</v>
       </c>
-      <c r="C30" s="3" t="s">
+      <c r="C30" s="30" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="31" spans="1:3" ht="16" x14ac:dyDescent="0.4">
-      <c r="A31" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B31" s="32" t="s">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A31" s="30" t="s">
+        <v>4</v>
+      </c>
+      <c r="B31" s="30" t="s">
         <v>92</v>
       </c>
-      <c r="C31" s="3" t="s">
+      <c r="C31" s="30" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="32" spans="1:3" ht="16" x14ac:dyDescent="0.4">
-      <c r="A32" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B32" s="32" t="s">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A32" s="30" t="s">
+        <v>4</v>
+      </c>
+      <c r="B32" s="30" t="s">
         <v>92</v>
       </c>
-      <c r="C32" s="32" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" ht="16" x14ac:dyDescent="0.4">
-      <c r="A33" s="33" t="s">
-        <v>4</v>
-      </c>
-      <c r="B33" s="34" t="s">
+      <c r="C32" s="30" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A33" s="30" t="s">
+        <v>4</v>
+      </c>
+      <c r="B33" s="30" t="s">
         <v>178</v>
       </c>
-      <c r="C33" s="34" t="s">
+      <c r="C33" s="30" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="34" spans="1:3" ht="16" x14ac:dyDescent="0.4">
-      <c r="A34" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B34" s="32" t="s">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A34" s="30" t="s">
+        <v>4</v>
+      </c>
+      <c r="B34" s="30" t="s">
         <v>87</v>
       </c>
-      <c r="C34" s="3" t="s">
+      <c r="C34" s="30" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="35" spans="1:3" ht="16" x14ac:dyDescent="0.4">
-      <c r="A35" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B35" s="32" t="s">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A35" s="30" t="s">
+        <v>4</v>
+      </c>
+      <c r="B35" s="30" t="s">
         <v>87</v>
       </c>
-      <c r="C35" s="3" t="s">
+      <c r="C35" s="30" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="36" spans="1:3" ht="16" x14ac:dyDescent="0.4">
-      <c r="A36" s="33" t="s">
-        <v>4</v>
-      </c>
-      <c r="B36" s="34" t="s">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A36" s="30" t="s">
+        <v>4</v>
+      </c>
+      <c r="B36" s="30" t="s">
         <v>87</v>
       </c>
-      <c r="C36" s="35" t="s">
+      <c r="C36" s="30" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="37" spans="1:3" ht="16" x14ac:dyDescent="0.4">
-      <c r="A37" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B37" s="32" t="s">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A37" s="30" t="s">
+        <v>4</v>
+      </c>
+      <c r="B37" s="30" t="s">
         <v>87</v>
       </c>
-      <c r="C37" s="3" t="s">
+      <c r="C37" s="30" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="38" spans="1:3" ht="16" x14ac:dyDescent="0.4">
-      <c r="A38" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B38" s="32" t="s">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A38" s="30" t="s">
+        <v>4</v>
+      </c>
+      <c r="B38" s="30" t="s">
         <v>87</v>
       </c>
-      <c r="C38" s="3" t="s">
+      <c r="C38" s="30" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="39" spans="1:3" ht="16" x14ac:dyDescent="0.4">
-      <c r="A39" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B39" s="32" t="s">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A39" s="30" t="s">
+        <v>4</v>
+      </c>
+      <c r="B39" s="30" t="s">
         <v>87</v>
       </c>
-      <c r="C39" s="3" t="s">
+      <c r="C39" s="30" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="40" spans="1:3" ht="16" x14ac:dyDescent="0.4">
-      <c r="A40" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B40" s="32" t="s">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A40" s="30" t="s">
+        <v>4</v>
+      </c>
+      <c r="B40" s="30" t="s">
         <v>87</v>
       </c>
-      <c r="C40" s="3" t="s">
+      <c r="C40" s="30" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="41" spans="1:3" ht="16" x14ac:dyDescent="0.4">
-      <c r="A41" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B41" s="32" t="s">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A41" s="30" t="s">
+        <v>4</v>
+      </c>
+      <c r="B41" s="30" t="s">
         <v>87</v>
       </c>
-      <c r="C41" s="32" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" ht="16" x14ac:dyDescent="0.4">
-      <c r="A42" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B42" s="32" t="s">
+      <c r="C41" s="30" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A42" s="30" t="s">
+        <v>4</v>
+      </c>
+      <c r="B42" s="30" t="s">
         <v>106</v>
       </c>
-      <c r="C42" s="3" t="s">
+      <c r="C42" s="30" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="43" spans="1:3" ht="16" x14ac:dyDescent="0.4">
-      <c r="A43" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B43" s="32" t="s">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A43" s="30" t="s">
+        <v>4</v>
+      </c>
+      <c r="B43" s="30" t="s">
         <v>106</v>
       </c>
-      <c r="C43" s="3" t="s">
+      <c r="C43" s="30" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="44" spans="1:3" ht="16" x14ac:dyDescent="0.4">
-      <c r="A44" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B44" s="32" t="s">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A44" s="30" t="s">
+        <v>4</v>
+      </c>
+      <c r="B44" s="30" t="s">
         <v>106</v>
       </c>
-      <c r="C44" s="3" t="s">
+      <c r="C44" s="30" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="45" spans="1:3" ht="16" x14ac:dyDescent="0.4">
-      <c r="A45" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B45" s="32" t="s">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A45" s="30" t="s">
+        <v>4</v>
+      </c>
+      <c r="B45" s="30" t="s">
         <v>106</v>
       </c>
-      <c r="C45" s="3" t="s">
+      <c r="C45" s="30" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="46" spans="1:3" ht="16" x14ac:dyDescent="0.4">
-      <c r="A46" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B46" s="32" t="s">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A46" s="30" t="s">
+        <v>4</v>
+      </c>
+      <c r="B46" s="30" t="s">
         <v>106</v>
       </c>
-      <c r="C46" s="3" t="s">
+      <c r="C46" s="30" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="47" spans="1:3" ht="16" x14ac:dyDescent="0.4">
-      <c r="A47" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B47" s="32" t="s">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A47" s="30" t="s">
+        <v>4</v>
+      </c>
+      <c r="B47" s="30" t="s">
         <v>106</v>
       </c>
-      <c r="C47" s="3" t="s">
+      <c r="C47" s="30" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="48" spans="1:3" ht="16" x14ac:dyDescent="0.4">
-      <c r="A48" s="33" t="s">
-        <v>4</v>
-      </c>
-      <c r="B48" s="34" t="s">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A48" s="30" t="s">
+        <v>4</v>
+      </c>
+      <c r="B48" s="30" t="s">
         <v>106</v>
       </c>
-      <c r="C48" s="35" t="s">
+      <c r="C48" s="30" t="s">
         <v>283</v>
       </c>
     </row>
-    <row r="49" spans="1:3" ht="16" x14ac:dyDescent="0.4">
-      <c r="A49" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B49" s="32" t="s">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A49" s="30" t="s">
+        <v>4</v>
+      </c>
+      <c r="B49" s="30" t="s">
         <v>106</v>
       </c>
-      <c r="C49" s="3" t="s">
+      <c r="C49" s="30" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="50" spans="1:3" ht="16" x14ac:dyDescent="0.4">
-      <c r="A50" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B50" s="32" t="s">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A50" s="30" t="s">
+        <v>4</v>
+      </c>
+      <c r="B50" s="30" t="s">
         <v>106</v>
       </c>
-      <c r="C50" s="32" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" ht="16" x14ac:dyDescent="0.4">
-      <c r="A51" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B51" s="32" t="s">
+      <c r="C50" s="30" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A51" s="30" t="s">
+        <v>4</v>
+      </c>
+      <c r="B51" s="30" t="s">
         <v>111</v>
       </c>
-      <c r="C51" s="3" t="s">
+      <c r="C51" s="30" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="52" spans="1:3" ht="16" x14ac:dyDescent="0.4">
-      <c r="A52" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B52" s="32" t="s">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A52" s="30" t="s">
+        <v>4</v>
+      </c>
+      <c r="B52" s="30" t="s">
         <v>111</v>
       </c>
-      <c r="C52" s="3" t="s">
+      <c r="C52" s="30" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="53" spans="1:3" ht="16" x14ac:dyDescent="0.4">
-      <c r="A53" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B53" s="32" t="s">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A53" s="30" t="s">
+        <v>4</v>
+      </c>
+      <c r="B53" s="30" t="s">
         <v>111</v>
       </c>
-      <c r="C53" s="3" t="s">
+      <c r="C53" s="30" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="54" spans="1:3" ht="16" x14ac:dyDescent="0.4">
-      <c r="A54" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B54" s="32" t="s">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A54" s="30" t="s">
+        <v>4</v>
+      </c>
+      <c r="B54" s="30" t="s">
         <v>111</v>
       </c>
-      <c r="C54" s="3" t="s">
+      <c r="C54" s="30" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="55" spans="1:3" ht="16" x14ac:dyDescent="0.4">
-      <c r="A55" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B55" s="32" t="s">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A55" s="30" t="s">
+        <v>4</v>
+      </c>
+      <c r="B55" s="30" t="s">
         <v>111</v>
       </c>
-      <c r="C55" s="3" t="s">
+      <c r="C55" s="30" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="56" spans="1:3" ht="16" x14ac:dyDescent="0.4">
-      <c r="A56" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B56" s="32" t="s">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A56" s="30" t="s">
+        <v>4</v>
+      </c>
+      <c r="B56" s="30" t="s">
         <v>111</v>
       </c>
-      <c r="C56" s="3" t="s">
+      <c r="C56" s="30" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="57" spans="1:3" ht="16" x14ac:dyDescent="0.4">
-      <c r="A57" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B57" s="32" t="s">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A57" s="30" t="s">
+        <v>4</v>
+      </c>
+      <c r="B57" s="30" t="s">
         <v>111</v>
       </c>
-      <c r="C57" s="3" t="s">
+      <c r="C57" s="30" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="58" spans="1:3" ht="16" x14ac:dyDescent="0.4">
-      <c r="A58" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B58" s="32" t="s">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A58" s="30" t="s">
+        <v>4</v>
+      </c>
+      <c r="B58" s="30" t="s">
         <v>111</v>
       </c>
-      <c r="C58" s="3" t="s">
+      <c r="C58" s="30" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="59" spans="1:3" ht="16" x14ac:dyDescent="0.4">
-      <c r="A59" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B59" s="32" t="s">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A59" s="30" t="s">
+        <v>4</v>
+      </c>
+      <c r="B59" s="30" t="s">
         <v>111</v>
       </c>
-      <c r="C59" s="3" t="s">
+      <c r="C59" s="30" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="60" spans="1:3" ht="16" x14ac:dyDescent="0.4">
-      <c r="A60" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B60" s="32" t="s">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A60" s="30" t="s">
+        <v>4</v>
+      </c>
+      <c r="B60" s="30" t="s">
         <v>111</v>
       </c>
-      <c r="C60" s="3" t="s">
+      <c r="C60" s="30" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="61" spans="1:3" ht="16" x14ac:dyDescent="0.4">
-      <c r="A61" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B61" s="32" t="s">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A61" s="30" t="s">
+        <v>4</v>
+      </c>
+      <c r="B61" s="30" t="s">
         <v>111</v>
       </c>
-      <c r="C61" s="3" t="s">
+      <c r="C61" s="30" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="62" spans="1:3" ht="16" x14ac:dyDescent="0.4">
-      <c r="A62" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B62" s="32" t="s">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A62" s="30" t="s">
+        <v>4</v>
+      </c>
+      <c r="B62" s="30" t="s">
         <v>111</v>
       </c>
-      <c r="C62" s="3" t="s">
+      <c r="C62" s="30" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="63" spans="1:3" ht="16" x14ac:dyDescent="0.4">
-      <c r="A63" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B63" s="32" t="s">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A63" s="30" t="s">
+        <v>4</v>
+      </c>
+      <c r="B63" s="30" t="s">
         <v>111</v>
       </c>
-      <c r="C63" s="3" t="s">
+      <c r="C63" s="30" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="64" spans="1:3" ht="16" x14ac:dyDescent="0.4">
-      <c r="A64" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B64" s="32" t="s">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A64" s="30" t="s">
+        <v>4</v>
+      </c>
+      <c r="B64" s="30" t="s">
         <v>111</v>
       </c>
-      <c r="C64" s="3" t="s">
+      <c r="C64" s="30" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="65" spans="1:3" ht="16" x14ac:dyDescent="0.4">
-      <c r="A65" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B65" s="32" t="s">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A65" s="30" t="s">
+        <v>4</v>
+      </c>
+      <c r="B65" s="30" t="s">
         <v>111</v>
       </c>
-      <c r="C65" s="32" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="66" spans="1:3" ht="16" x14ac:dyDescent="0.4">
-      <c r="A66" s="33" t="s">
-        <v>4</v>
-      </c>
-      <c r="B66" s="34" t="s">
+      <c r="C65" s="30" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A66" s="30" t="s">
+        <v>4</v>
+      </c>
+      <c r="B66" s="30" t="s">
         <v>284</v>
       </c>
-      <c r="C66" s="34" t="s">
+      <c r="C66" s="30" t="s">
         <v>284</v>
       </c>
     </row>
-    <row r="67" spans="1:3" ht="16" x14ac:dyDescent="0.4">
-      <c r="A67" s="33" t="s">
-        <v>4</v>
-      </c>
-      <c r="B67" s="34" t="s">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A67" s="30" t="s">
+        <v>4</v>
+      </c>
+      <c r="B67" s="30" t="s">
         <v>266</v>
       </c>
-      <c r="C67" s="34" t="s">
+      <c r="C67" s="30" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="68" spans="1:3" ht="16" x14ac:dyDescent="0.4">
-      <c r="A68" s="33" t="s">
-        <v>4</v>
-      </c>
-      <c r="B68" s="34" t="s">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A68" s="30" t="s">
+        <v>4</v>
+      </c>
+      <c r="B68" s="30" t="s">
         <v>266</v>
       </c>
-      <c r="C68" s="34" t="s">
+      <c r="C68" s="30" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="69" spans="1:3" ht="16" x14ac:dyDescent="0.4">
-      <c r="A69" s="33" t="s">
-        <v>4</v>
-      </c>
-      <c r="B69" s="34" t="s">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A69" s="30" t="s">
+        <v>4</v>
+      </c>
+      <c r="B69" s="30" t="s">
         <v>266</v>
       </c>
-      <c r="C69" s="34" t="s">
+      <c r="C69" s="30" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="70" spans="1:3" ht="16" x14ac:dyDescent="0.4">
-      <c r="A70" s="33" t="s">
-        <v>4</v>
-      </c>
-      <c r="B70" s="34" t="s">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A70" s="30" t="s">
+        <v>4</v>
+      </c>
+      <c r="B70" s="30" t="s">
         <v>266</v>
       </c>
-      <c r="C70" s="34" t="s">
+      <c r="C70" s="30" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="71" spans="1:3" ht="16" x14ac:dyDescent="0.4">
-      <c r="A71" s="33" t="s">
-        <v>4</v>
-      </c>
-      <c r="B71" s="34" t="s">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A71" s="30" t="s">
+        <v>4</v>
+      </c>
+      <c r="B71" s="30" t="s">
         <v>266</v>
       </c>
-      <c r="C71" s="34" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="72" spans="1:3" ht="16" x14ac:dyDescent="0.4">
-      <c r="A72" s="33" t="s">
-        <v>4</v>
-      </c>
-      <c r="B72" s="34" t="s">
+      <c r="C71" s="30" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A72" s="30" t="s">
+        <v>4</v>
+      </c>
+      <c r="B72" s="30" t="s">
         <v>285</v>
       </c>
-      <c r="C72" s="34" t="s">
+      <c r="C72" s="30" t="s">
         <v>285</v>
       </c>
     </row>
-    <row r="73" spans="1:3" ht="16" x14ac:dyDescent="0.4">
-      <c r="A73" s="33" t="s">
-        <v>4</v>
-      </c>
-      <c r="B73" s="34" t="s">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A73" s="30" t="s">
+        <v>4</v>
+      </c>
+      <c r="B73" s="30" t="s">
         <v>286</v>
       </c>
-      <c r="C73" s="34" t="s">
+      <c r="C73" s="30" t="s">
         <v>286</v>
       </c>
     </row>
-    <row r="74" spans="1:3" ht="16" x14ac:dyDescent="0.4">
-      <c r="A74" s="33" t="s">
-        <v>4</v>
-      </c>
-      <c r="B74" s="34" t="s">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A74" s="30" t="s">
+        <v>4</v>
+      </c>
+      <c r="B74" s="30" t="s">
         <v>149</v>
       </c>
-      <c r="C74" s="34" t="s">
+      <c r="C74" s="30" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="75" spans="1:3" ht="16" x14ac:dyDescent="0.4">
-      <c r="A75" s="1" t="s">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A75" s="31" t="s">
+        <v>4</v>
+      </c>
+      <c r="B75" s="31" t="s">
+        <v>291</v>
+      </c>
+      <c r="C75" s="31" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A76" s="31" t="s">
+        <v>4</v>
+      </c>
+      <c r="B76" s="31" t="s">
+        <v>291</v>
+      </c>
+      <c r="C76" s="31" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A77" s="31" t="s">
+        <v>4</v>
+      </c>
+      <c r="B77" s="31" t="s">
+        <v>291</v>
+      </c>
+      <c r="C77" s="31" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A78" s="31" t="s">
+        <v>4</v>
+      </c>
+      <c r="B78" s="31" t="s">
+        <v>291</v>
+      </c>
+      <c r="C78" s="31" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A79" s="31" t="s">
+        <v>4</v>
+      </c>
+      <c r="B79" s="31" t="s">
+        <v>291</v>
+      </c>
+      <c r="C79" s="31" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A80" s="31" t="s">
+        <v>4</v>
+      </c>
+      <c r="B80" s="31" t="s">
+        <v>295</v>
+      </c>
+      <c r="C80" s="31" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A81" s="31" t="s">
+        <v>4</v>
+      </c>
+      <c r="B81" s="31" t="s">
+        <v>295</v>
+      </c>
+      <c r="C81" s="31" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A82" s="31" t="s">
+        <v>4</v>
+      </c>
+      <c r="B82" s="31" t="s">
+        <v>295</v>
+      </c>
+      <c r="C82" s="31" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A83" s="31" t="s">
+        <v>4</v>
+      </c>
+      <c r="B83" s="31" t="s">
+        <v>295</v>
+      </c>
+      <c r="C83" s="31" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A84" s="31" t="s">
+        <v>4</v>
+      </c>
+      <c r="B84" s="31" t="s">
+        <v>295</v>
+      </c>
+      <c r="C84" s="31" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A85" s="31" t="s">
+        <v>4</v>
+      </c>
+      <c r="B85" s="31" t="s">
+        <v>299</v>
+      </c>
+      <c r="C85" s="31" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A86" s="30" t="s">
         <v>153</v>
       </c>
-      <c r="B75" s="32" t="s">
+      <c r="B86" s="30" t="s">
         <v>187</v>
       </c>
-      <c r="C75" s="3" t="s">
+      <c r="C86" s="30" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="76" spans="1:3" ht="16" x14ac:dyDescent="0.4">
-      <c r="A76" s="1" t="s">
+    <row r="87" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A87" s="30" t="s">
         <v>153</v>
       </c>
-      <c r="B76" s="32" t="s">
+      <c r="B87" s="30" t="s">
         <v>189</v>
       </c>
-      <c r="C76" s="3" t="s">
+      <c r="C87" s="30" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="77" spans="1:3" ht="16" x14ac:dyDescent="0.4">
-      <c r="A77" s="1" t="s">
+    <row r="88" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A88" s="30" t="s">
         <v>153</v>
       </c>
-      <c r="B77" s="32" t="s">
+      <c r="B88" s="30" t="s">
         <v>189</v>
       </c>
-      <c r="C77" s="3" t="s">
+      <c r="C88" s="30" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="78" spans="1:3" ht="16" x14ac:dyDescent="0.4">
-      <c r="A78" s="1" t="s">
+    <row r="89" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A89" s="30" t="s">
         <v>153</v>
       </c>
-      <c r="B78" s="32" t="s">
+      <c r="B89" s="30" t="s">
         <v>189</v>
       </c>
-      <c r="C78" s="3" t="s">
+      <c r="C89" s="30" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="79" spans="1:3" ht="32" x14ac:dyDescent="0.4">
-      <c r="A79" s="1" t="s">
+    <row r="90" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A90" s="30" t="s">
         <v>153</v>
       </c>
-      <c r="B79" s="32" t="s">
+      <c r="B90" s="30" t="s">
         <v>189</v>
       </c>
-      <c r="C79" s="3" t="s">
+      <c r="C90" s="30" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="80" spans="1:3" ht="16" x14ac:dyDescent="0.4">
-      <c r="A80" s="1" t="s">
+    <row r="91" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A91" s="30" t="s">
         <v>153</v>
       </c>
-      <c r="B80" s="32" t="s">
+      <c r="B91" s="30" t="s">
         <v>194</v>
       </c>
-      <c r="C80" s="32" t="s">
+      <c r="C91" s="30" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="81" spans="1:3" ht="16" x14ac:dyDescent="0.4">
-      <c r="A81" s="1" t="s">
+    <row r="92" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A92" s="30" t="s">
         <v>153</v>
       </c>
-      <c r="B81" s="32" t="s">
-        <v>79</v>
-      </c>
-      <c r="C81" s="32" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="82" spans="1:3" ht="16" x14ac:dyDescent="0.4">
-      <c r="A82" s="1" t="s">
+      <c r="B92" s="30" t="s">
+        <v>79</v>
+      </c>
+      <c r="C92" s="30" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A93" s="30" t="s">
         <v>154</v>
       </c>
-      <c r="B82" s="32" t="s">
+      <c r="B93" s="30" t="s">
         <v>195</v>
       </c>
-      <c r="C82" s="32" t="s">
+      <c r="C93" s="30" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="83" spans="1:3" ht="16" x14ac:dyDescent="0.4">
-      <c r="A83" s="1" t="s">
+    <row r="94" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A94" s="30" t="s">
         <v>154</v>
       </c>
-      <c r="B83" s="32" t="s">
+      <c r="B94" s="30" t="s">
         <v>196</v>
       </c>
-      <c r="C83" s="32" t="s">
+      <c r="C94" s="30" t="s">
         <v>196</v>
       </c>
     </row>
-    <row r="84" spans="1:3" ht="16" x14ac:dyDescent="0.4">
-      <c r="A84" s="1" t="s">
+    <row r="95" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A95" s="30" t="s">
         <v>154</v>
       </c>
-      <c r="B84" s="32" t="s">
+      <c r="B95" s="30" t="s">
         <v>197</v>
       </c>
-      <c r="C84" s="32" t="s">
+      <c r="C95" s="30" t="s">
         <v>197</v>
       </c>
     </row>
-    <row r="85" spans="1:3" ht="16" x14ac:dyDescent="0.4">
-      <c r="A85" s="1" t="s">
+    <row r="96" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A96" s="30" t="s">
         <v>154</v>
       </c>
-      <c r="B85" s="32" t="s">
+      <c r="B96" s="30" t="s">
         <v>198</v>
       </c>
-      <c r="C85" s="32" t="s">
+      <c r="C96" s="30" t="s">
         <v>198</v>
       </c>
     </row>
-    <row r="86" spans="1:3" ht="16" x14ac:dyDescent="0.4">
-      <c r="A86" s="33" t="s">
+    <row r="97" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A97" s="30" t="s">
         <v>154</v>
       </c>
-      <c r="B86" s="34" t="s">
+      <c r="B97" s="30" t="s">
         <v>287</v>
       </c>
-      <c r="C86" s="34" t="s">
+      <c r="C97" s="30" t="s">
         <v>287</v>
       </c>
     </row>
-    <row r="87" spans="1:3" ht="16" x14ac:dyDescent="0.4">
-      <c r="A87" s="33" t="s">
+    <row r="98" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A98" s="30" t="s">
         <v>154</v>
       </c>
-      <c r="B87" s="34" t="s">
+      <c r="B98" s="30" t="s">
         <v>288</v>
       </c>
-      <c r="C87" s="34" t="s">
+      <c r="C98" s="30" t="s">
         <v>288</v>
       </c>
     </row>
-    <row r="88" spans="1:3" ht="16" x14ac:dyDescent="0.4">
-      <c r="A88" s="1" t="s">
+    <row r="99" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A99" s="30" t="s">
         <v>154</v>
       </c>
-      <c r="B88" s="32" t="s">
-        <v>79</v>
-      </c>
-      <c r="C88" s="32" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="89" spans="1:3" ht="16" x14ac:dyDescent="0.4">
-      <c r="A89" s="1" t="s">
+      <c r="B99" s="30" t="s">
+        <v>79</v>
+      </c>
+      <c r="C99" s="30" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A100" s="30" t="s">
         <v>199</v>
       </c>
-      <c r="B89" s="32" t="s">
+      <c r="B100" s="30" t="s">
         <v>200</v>
       </c>
-      <c r="C89" s="32" t="s">
+      <c r="C100" s="30" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="90" spans="1:3" ht="16" x14ac:dyDescent="0.4">
-      <c r="A90" s="1" t="s">
+    <row r="101" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A101" s="30" t="s">
         <v>199</v>
       </c>
-      <c r="B90" s="32" t="s">
-        <v>79</v>
-      </c>
-      <c r="C90" s="32" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="91" spans="1:3" ht="16" x14ac:dyDescent="0.4">
-      <c r="A91" s="1" t="s">
+      <c r="B101" s="30" t="s">
+        <v>79</v>
+      </c>
+      <c r="C101" s="30" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A102" s="30" t="s">
         <v>85</v>
       </c>
-      <c r="B91" s="32" t="s">
+      <c r="B102" s="30" t="s">
         <v>63</v>
       </c>
-      <c r="C91" s="32" t="s">
+      <c r="C102" s="30" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="92" spans="1:3" ht="16" x14ac:dyDescent="0.4">
-      <c r="A92" s="33" t="s">
+    <row r="103" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A103" s="30" t="s">
         <v>85</v>
       </c>
-      <c r="B92" s="34" t="s">
+      <c r="B103" s="30" t="s">
         <v>63</v>
       </c>
-      <c r="C92" s="34" t="s">
+      <c r="C103" s="30" t="s">
         <v>289</v>
       </c>
     </row>
-    <row r="93" spans="1:3" ht="16" x14ac:dyDescent="0.4">
-      <c r="A93" s="1" t="s">
+    <row r="104" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A104" s="30" t="s">
         <v>85</v>
       </c>
-      <c r="B93" s="32" t="s">
+      <c r="B104" s="30" t="s">
         <v>63</v>
       </c>
-      <c r="C93" s="32" t="s">
+      <c r="C104" s="30" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="94" spans="1:3" ht="16" x14ac:dyDescent="0.4">
-      <c r="A94" s="1" t="s">
+    <row r="105" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A105" s="30" t="s">
         <v>85</v>
       </c>
-      <c r="B94" s="32" t="s">
+      <c r="B105" s="30" t="s">
         <v>76</v>
       </c>
-      <c r="C94" s="32" t="s">
+      <c r="C105" s="30" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="95" spans="1:3" ht="16" x14ac:dyDescent="0.4">
-      <c r="A95" s="1" t="s">
+    <row r="106" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A106" s="30" t="s">
         <v>85</v>
       </c>
-      <c r="B95" s="32" t="s">
+      <c r="B106" s="30" t="s">
         <v>76</v>
       </c>
-      <c r="C95" s="32" t="s">
+      <c r="C106" s="30" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="96" spans="1:3" ht="16" x14ac:dyDescent="0.4">
-      <c r="A96" s="1" t="s">
+    <row r="107" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A107" s="30" t="s">
         <v>85</v>
       </c>
-      <c r="B96" s="32" t="s">
+      <c r="B107" s="30" t="s">
         <v>76</v>
       </c>
-      <c r="C96" s="32" t="s">
+      <c r="C107" s="30" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="97" spans="1:3" ht="16" x14ac:dyDescent="0.4">
-      <c r="A97" s="1" t="s">
+    <row r="108" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A108" s="30" t="s">
         <v>85</v>
       </c>
-      <c r="B97" s="32" t="s">
-        <v>79</v>
-      </c>
-      <c r="C97" s="32" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="98" spans="1:3" ht="16" x14ac:dyDescent="0.4">
-      <c r="A98" s="36" t="s">
+      <c r="B108" s="30" t="s">
+        <v>79</v>
+      </c>
+      <c r="C108" s="30" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A109" s="30" t="s">
         <v>290</v>
       </c>
-      <c r="B98" s="37" t="s">
+      <c r="B109" s="30" t="s">
         <v>290</v>
       </c>
-      <c r="C98" s="37" t="s">
+      <c r="C109" s="30" t="s">
         <v>290</v>
       </c>
     </row>
@@ -5538,1143 +6136,1143 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{879FCB13-5648-4E3C-9870-AC07540F3365}">
   <dimension ref="A1:C103"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.7265625" customWidth="1"/>
-    <col min="2" max="2" width="27.26953125" customWidth="1"/>
+    <col min="1" max="1" width="19.77734375" customWidth="1"/>
+    <col min="2" max="2" width="27.21875" customWidth="1"/>
     <col min="3" max="3" width="39" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A1" s="29" t="s">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="27" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="30" t="s">
+      <c r="B1" s="28" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="30" t="s">
+      <c r="C1" s="28" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A2" s="26" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" s="26" t="s">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="24" t="s">
         <v>92</v>
       </c>
-      <c r="C2" s="26" t="s">
+      <c r="C2" s="24" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A3" s="26" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="26" t="s">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="24" t="s">
         <v>92</v>
       </c>
-      <c r="C3" s="26" t="s">
+      <c r="C3" s="24" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A4" s="26" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" s="26" t="s">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="24" t="s">
         <v>92</v>
       </c>
-      <c r="C4" s="26" t="s">
+      <c r="C4" s="24" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A5" s="26" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5" s="26" t="s">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="24" t="s">
         <v>92</v>
       </c>
-      <c r="C5" s="27" t="s">
+      <c r="C5" s="25" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A6" s="26" t="s">
-        <v>4</v>
-      </c>
-      <c r="B6" s="26" t="s">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="24" t="s">
         <v>92</v>
       </c>
-      <c r="C6" s="26" t="s">
+      <c r="C6" s="24" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A7" s="26" t="s">
-        <v>4</v>
-      </c>
-      <c r="B7" s="26" t="s">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7" s="24" t="s">
         <v>92</v>
       </c>
-      <c r="C7" s="26" t="s">
+      <c r="C7" s="24" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A8" s="26" t="s">
-        <v>4</v>
-      </c>
-      <c r="B8" s="26" t="s">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="B8" s="24" t="s">
         <v>92</v>
       </c>
-      <c r="C8" s="26" t="s">
+      <c r="C8" s="24" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A9" s="26" t="s">
-        <v>4</v>
-      </c>
-      <c r="B9" s="26" t="s">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="B9" s="24" t="s">
         <v>92</v>
       </c>
-      <c r="C9" s="26" t="s">
+      <c r="C9" s="24" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A10" s="26" t="s">
-        <v>4</v>
-      </c>
-      <c r="B10" s="26" t="s">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="B10" s="24" t="s">
         <v>92</v>
       </c>
-      <c r="C10" s="26" t="s">
+      <c r="C10" s="24" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A11" s="26" t="s">
-        <v>4</v>
-      </c>
-      <c r="B11" s="26" t="s">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="B11" s="24" t="s">
         <v>92</v>
       </c>
-      <c r="C11" s="26" t="s">
+      <c r="C11" s="24" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A12" s="26" t="s">
-        <v>4</v>
-      </c>
-      <c r="B12" s="26" t="s">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="B12" s="24" t="s">
         <v>92</v>
       </c>
-      <c r="C12" s="26" t="s">
+      <c r="C12" s="24" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A13" s="26" t="s">
-        <v>4</v>
-      </c>
-      <c r="B13" s="26" t="s">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="B13" s="24" t="s">
         <v>92</v>
       </c>
-      <c r="C13" s="26" t="s">
+      <c r="C13" s="24" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A14" s="26" t="s">
-        <v>4</v>
-      </c>
-      <c r="B14" s="26" t="s">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="B14" s="24" t="s">
         <v>92</v>
       </c>
-      <c r="C14" s="26" t="s">
+      <c r="C14" s="24" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A15" s="26" t="s">
-        <v>4</v>
-      </c>
-      <c r="B15" s="26" t="s">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A15" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="B15" s="24" t="s">
         <v>92</v>
       </c>
-      <c r="C15" s="26" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A16" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="B16" s="28" t="s">
+      <c r="C15" s="24" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A16" s="26" t="s">
+        <v>4</v>
+      </c>
+      <c r="B16" s="26" t="s">
         <v>87</v>
       </c>
-      <c r="C16" s="28" t="s">
+      <c r="C16" s="26" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A17" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="B17" s="28" t="s">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A17" s="26" t="s">
+        <v>4</v>
+      </c>
+      <c r="B17" s="26" t="s">
         <v>87</v>
       </c>
-      <c r="C17" s="28" t="s">
+      <c r="C17" s="26" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A18" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="B18" s="28" t="s">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A18" s="26" t="s">
+        <v>4</v>
+      </c>
+      <c r="B18" s="26" t="s">
         <v>87</v>
       </c>
-      <c r="C18" s="28" t="s">
+      <c r="C18" s="26" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A19" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="B19" s="28" t="s">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A19" s="26" t="s">
+        <v>4</v>
+      </c>
+      <c r="B19" s="26" t="s">
         <v>87</v>
       </c>
-      <c r="C19" s="28" t="s">
+      <c r="C19" s="26" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A20" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="B20" s="28" t="s">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A20" s="26" t="s">
+        <v>4</v>
+      </c>
+      <c r="B20" s="26" t="s">
         <v>87</v>
       </c>
-      <c r="C20" s="28" t="s">
+      <c r="C20" s="26" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A21" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="B21" s="28" t="s">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A21" s="26" t="s">
+        <v>4</v>
+      </c>
+      <c r="B21" s="26" t="s">
         <v>87</v>
       </c>
-      <c r="C21" s="28" t="s">
+      <c r="C21" s="26" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A22" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="B22" s="28" t="s">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A22" s="26" t="s">
+        <v>4</v>
+      </c>
+      <c r="B22" s="26" t="s">
         <v>87</v>
       </c>
-      <c r="C22" s="28" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A23" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="B23" s="28" t="s">
+      <c r="C22" s="26" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A23" s="26" t="s">
+        <v>4</v>
+      </c>
+      <c r="B23" s="26" t="s">
         <v>106</v>
       </c>
-      <c r="C23" s="28" t="s">
+      <c r="C23" s="26" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A24" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="B24" s="28" t="s">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A24" s="26" t="s">
+        <v>4</v>
+      </c>
+      <c r="B24" s="26" t="s">
         <v>106</v>
       </c>
-      <c r="C24" s="28" t="s">
+      <c r="C24" s="26" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A25" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="B25" s="28" t="s">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A25" s="26" t="s">
+        <v>4</v>
+      </c>
+      <c r="B25" s="26" t="s">
         <v>106</v>
       </c>
-      <c r="C25" s="28" t="s">
+      <c r="C25" s="26" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A26" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="B26" s="28" t="s">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A26" s="26" t="s">
+        <v>4</v>
+      </c>
+      <c r="B26" s="26" t="s">
         <v>106</v>
       </c>
-      <c r="C26" s="28" t="s">
+      <c r="C26" s="26" t="s">
         <v>210</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A27" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="B27" s="28" t="s">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A27" s="26" t="s">
+        <v>4</v>
+      </c>
+      <c r="B27" s="26" t="s">
         <v>106</v>
       </c>
-      <c r="C27" s="28" t="s">
+      <c r="C27" s="26" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A28" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="B28" s="28" t="s">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A28" s="26" t="s">
+        <v>4</v>
+      </c>
+      <c r="B28" s="26" t="s">
         <v>106</v>
       </c>
-      <c r="C28" s="28" t="s">
+      <c r="C28" s="26" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A29" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="B29" s="28" t="s">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A29" s="26" t="s">
+        <v>4</v>
+      </c>
+      <c r="B29" s="26" t="s">
         <v>106</v>
       </c>
-      <c r="C29" s="28" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A30" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="B30" s="28" t="s">
+      <c r="C29" s="26" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A30" s="26" t="s">
+        <v>4</v>
+      </c>
+      <c r="B30" s="26" t="s">
         <v>142</v>
       </c>
-      <c r="C30" s="28" t="s">
+      <c r="C30" s="26" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A31" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="B31" s="28" t="s">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A31" s="26" t="s">
+        <v>4</v>
+      </c>
+      <c r="B31" s="26" t="s">
         <v>142</v>
       </c>
-      <c r="C31" s="28" t="s">
+      <c r="C31" s="26" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A32" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="B32" s="28" t="s">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A32" s="26" t="s">
+        <v>4</v>
+      </c>
+      <c r="B32" s="26" t="s">
         <v>142</v>
       </c>
-      <c r="C32" s="28" t="s">
+      <c r="C32" s="26" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A33" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="B33" s="28" t="s">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A33" s="26" t="s">
+        <v>4</v>
+      </c>
+      <c r="B33" s="26" t="s">
         <v>142</v>
       </c>
-      <c r="C33" s="28" t="s">
+      <c r="C33" s="26" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A34" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="B34" s="28" t="s">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A34" s="26" t="s">
+        <v>4</v>
+      </c>
+      <c r="B34" s="26" t="s">
         <v>142</v>
       </c>
-      <c r="C34" s="28" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A35" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="B35" s="28" t="s">
+      <c r="C34" s="26" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A35" s="26" t="s">
+        <v>4</v>
+      </c>
+      <c r="B35" s="26" t="s">
         <v>146</v>
       </c>
-      <c r="C35" s="28" t="s">
+      <c r="C35" s="26" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A36" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="B36" s="28" t="s">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A36" s="26" t="s">
+        <v>4</v>
+      </c>
+      <c r="B36" s="26" t="s">
         <v>146</v>
       </c>
-      <c r="C36" s="28" t="s">
+      <c r="C36" s="26" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A37" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="B37" s="28" t="s">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A37" s="26" t="s">
+        <v>4</v>
+      </c>
+      <c r="B37" s="26" t="s">
         <v>146</v>
       </c>
-      <c r="C37" s="28" t="s">
+      <c r="C37" s="26" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A38" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="B38" s="28" t="s">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A38" s="26" t="s">
+        <v>4</v>
+      </c>
+      <c r="B38" s="26" t="s">
         <v>146</v>
       </c>
-      <c r="C38" s="28" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A39" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="B39" s="28" t="s">
+      <c r="C38" s="26" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A39" s="26" t="s">
+        <v>4</v>
+      </c>
+      <c r="B39" s="26" t="s">
         <v>111</v>
       </c>
-      <c r="C39" s="28" t="s">
+      <c r="C39" s="26" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A40" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="B40" s="28" t="s">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A40" s="26" t="s">
+        <v>4</v>
+      </c>
+      <c r="B40" s="26" t="s">
         <v>111</v>
       </c>
-      <c r="C40" s="28" t="s">
+      <c r="C40" s="26" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A41" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="B41" s="28" t="s">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A41" s="26" t="s">
+        <v>4</v>
+      </c>
+      <c r="B41" s="26" t="s">
         <v>111</v>
       </c>
-      <c r="C41" s="28" t="s">
+      <c r="C41" s="26" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A42" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="B42" s="28" t="s">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A42" s="26" t="s">
+        <v>4</v>
+      </c>
+      <c r="B42" s="26" t="s">
         <v>111</v>
       </c>
-      <c r="C42" s="28" t="s">
+      <c r="C42" s="26" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A43" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="B43" s="28" t="s">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A43" s="26" t="s">
+        <v>4</v>
+      </c>
+      <c r="B43" s="26" t="s">
         <v>111</v>
       </c>
-      <c r="C43" s="28" t="s">
+      <c r="C43" s="26" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A44" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="B44" s="28" t="s">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A44" s="26" t="s">
+        <v>4</v>
+      </c>
+      <c r="B44" s="26" t="s">
         <v>111</v>
       </c>
-      <c r="C44" s="28" t="s">
+      <c r="C44" s="26" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A45" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="B45" s="28" t="s">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A45" s="26" t="s">
+        <v>4</v>
+      </c>
+      <c r="B45" s="26" t="s">
         <v>111</v>
       </c>
-      <c r="C45" s="28" t="s">
+      <c r="C45" s="26" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A46" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="B46" s="28" t="s">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A46" s="26" t="s">
+        <v>4</v>
+      </c>
+      <c r="B46" s="26" t="s">
         <v>111</v>
       </c>
-      <c r="C46" s="28" t="s">
+      <c r="C46" s="26" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A47" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="B47" s="28" t="s">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A47" s="26" t="s">
+        <v>4</v>
+      </c>
+      <c r="B47" s="26" t="s">
         <v>111</v>
       </c>
-      <c r="C47" s="28" t="s">
+      <c r="C47" s="26" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A48" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="B48" s="28" t="s">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A48" s="26" t="s">
+        <v>4</v>
+      </c>
+      <c r="B48" s="26" t="s">
         <v>111</v>
       </c>
-      <c r="C48" s="28" t="s">
+      <c r="C48" s="26" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A49" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="B49" s="28" t="s">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A49" s="26" t="s">
+        <v>4</v>
+      </c>
+      <c r="B49" s="26" t="s">
         <v>111</v>
       </c>
-      <c r="C49" s="28" t="s">
+      <c r="C49" s="26" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A50" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="B50" s="28" t="s">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A50" s="26" t="s">
+        <v>4</v>
+      </c>
+      <c r="B50" s="26" t="s">
         <v>111</v>
       </c>
-      <c r="C50" s="28" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A51" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="B51" s="28" t="s">
+      <c r="C50" s="26" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A51" s="26" t="s">
+        <v>4</v>
+      </c>
+      <c r="B51" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="C51" s="28" t="s">
+      <c r="C51" s="26" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A52" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="B52" s="28" t="s">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A52" s="26" t="s">
+        <v>4</v>
+      </c>
+      <c r="B52" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="C52" s="28" t="s">
+      <c r="C52" s="26" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A53" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="B53" s="28" t="s">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A53" s="26" t="s">
+        <v>4</v>
+      </c>
+      <c r="B53" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="C53" s="28" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A54" s="28" t="s">
+      <c r="C53" s="26" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A54" s="26" t="s">
         <v>116</v>
       </c>
-      <c r="B54" s="28" t="s">
+      <c r="B54" s="26" t="s">
         <v>219</v>
       </c>
-      <c r="C54" s="28" t="s">
+      <c r="C54" s="26" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A55" s="28" t="s">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A55" s="26" t="s">
         <v>116</v>
       </c>
-      <c r="B55" s="28" t="s">
+      <c r="B55" s="26" t="s">
         <v>219</v>
       </c>
-      <c r="C55" s="28" t="s">
+      <c r="C55" s="26" t="s">
         <v>221</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A56" s="28" t="s">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A56" s="26" t="s">
         <v>116</v>
       </c>
-      <c r="B56" s="28" t="s">
+      <c r="B56" s="26" t="s">
         <v>219</v>
       </c>
-      <c r="C56" s="28" t="s">
+      <c r="C56" s="26" t="s">
         <v>222</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A57" s="28" t="s">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A57" s="26" t="s">
         <v>116</v>
       </c>
-      <c r="B57" s="28" t="s">
+      <c r="B57" s="26" t="s">
         <v>219</v>
       </c>
-      <c r="C57" s="28" t="s">
+      <c r="C57" s="26" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A58" s="28" t="s">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A58" s="26" t="s">
         <v>116</v>
       </c>
-      <c r="B58" s="28" t="s">
+      <c r="B58" s="26" t="s">
         <v>219</v>
       </c>
-      <c r="C58" s="28" t="s">
+      <c r="C58" s="26" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A59" s="28" t="s">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A59" s="26" t="s">
         <v>116</v>
       </c>
-      <c r="B59" s="28" t="s">
+      <c r="B59" s="26" t="s">
         <v>219</v>
       </c>
-      <c r="C59" s="28" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A60" s="28" t="s">
+      <c r="C59" s="26" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A60" s="26" t="s">
         <v>116</v>
       </c>
-      <c r="B60" s="28" t="s">
+      <c r="B60" s="26" t="s">
         <v>225</v>
       </c>
-      <c r="C60" s="28" t="s">
+      <c r="C60" s="26" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A61" s="28" t="s">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A61" s="26" t="s">
         <v>116</v>
       </c>
-      <c r="B61" s="28" t="s">
+      <c r="B61" s="26" t="s">
         <v>225</v>
       </c>
-      <c r="C61" s="28" t="s">
+      <c r="C61" s="26" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A62" s="28" t="s">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A62" s="26" t="s">
         <v>116</v>
       </c>
-      <c r="B62" s="28" t="s">
+      <c r="B62" s="26" t="s">
         <v>225</v>
       </c>
-      <c r="C62" s="28" t="s">
+      <c r="C62" s="26" t="s">
         <v>228</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A63" s="28" t="s">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A63" s="26" t="s">
         <v>116</v>
       </c>
-      <c r="B63" s="28" t="s">
+      <c r="B63" s="26" t="s">
         <v>225</v>
       </c>
-      <c r="C63" s="28" t="s">
+      <c r="C63" s="26" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A64" s="28" t="s">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A64" s="26" t="s">
         <v>116</v>
       </c>
-      <c r="B64" s="28" t="s">
+      <c r="B64" s="26" t="s">
         <v>225</v>
       </c>
-      <c r="C64" s="28" t="s">
+      <c r="C64" s="26" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A65" s="28" t="s">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A65" s="26" t="s">
         <v>116</v>
       </c>
-      <c r="B65" s="28" t="s">
+      <c r="B65" s="26" t="s">
         <v>225</v>
       </c>
-      <c r="C65" s="28" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A66" s="28" t="s">
+      <c r="C65" s="26" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A66" s="26" t="s">
         <v>116</v>
       </c>
-      <c r="B66" s="28" t="s">
+      <c r="B66" s="26" t="s">
         <v>231</v>
       </c>
-      <c r="C66" s="28" t="s">
+      <c r="C66" s="26" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A67" s="28" t="s">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A67" s="26" t="s">
         <v>116</v>
       </c>
-      <c r="B67" s="28" t="s">
+      <c r="B67" s="26" t="s">
         <v>231</v>
       </c>
-      <c r="C67" s="28" t="s">
+      <c r="C67" s="26" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A68" s="28" t="s">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A68" s="26" t="s">
         <v>116</v>
       </c>
-      <c r="B68" s="28" t="s">
+      <c r="B68" s="26" t="s">
         <v>231</v>
       </c>
-      <c r="C68" s="28" t="s">
+      <c r="C68" s="26" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A69" s="28" t="s">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A69" s="26" t="s">
         <v>116</v>
       </c>
-      <c r="B69" s="28" t="s">
+      <c r="B69" s="26" t="s">
         <v>231</v>
       </c>
-      <c r="C69" s="28" t="s">
+      <c r="C69" s="26" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A70" s="28" t="s">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A70" s="26" t="s">
         <v>116</v>
       </c>
-      <c r="B70" s="28" t="s">
+      <c r="B70" s="26" t="s">
         <v>231</v>
       </c>
-      <c r="C70" s="28" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A71" s="28" t="s">
+      <c r="C70" s="26" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A71" s="26" t="s">
         <v>84</v>
       </c>
-      <c r="B71" s="28" t="s">
+      <c r="B71" s="26" t="s">
         <v>233</v>
       </c>
-      <c r="C71" s="28" t="s">
+      <c r="C71" s="26" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A72" s="28" t="s">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A72" s="26" t="s">
         <v>84</v>
       </c>
-      <c r="B72" s="28" t="s">
+      <c r="B72" s="26" t="s">
         <v>234</v>
       </c>
-      <c r="C72" s="28" t="s">
+      <c r="C72" s="26" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A73" s="28" t="s">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A73" s="26" t="s">
         <v>84</v>
       </c>
-      <c r="B73" s="28" t="s">
+      <c r="B73" s="26" t="s">
         <v>235</v>
       </c>
-      <c r="C73" s="28" t="s">
+      <c r="C73" s="26" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A74" s="28" t="s">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A74" s="26" t="s">
         <v>75</v>
       </c>
-      <c r="B74" s="28" t="s">
+      <c r="B74" s="26" t="s">
         <v>124</v>
       </c>
-      <c r="C74" s="28" t="s">
+      <c r="C74" s="26" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A75" s="28" t="s">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A75" s="26" t="s">
         <v>75</v>
       </c>
-      <c r="B75" s="28" t="s">
+      <c r="B75" s="26" t="s">
         <v>125</v>
       </c>
-      <c r="C75" s="28" t="s">
+      <c r="C75" s="26" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A76" s="28" t="s">
+    <row r="76" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A76" s="26" t="s">
         <v>75</v>
       </c>
-      <c r="B76" s="28" t="s">
+      <c r="B76" s="26" t="s">
         <v>236</v>
       </c>
-      <c r="C76" s="28" t="s">
+      <c r="C76" s="26" t="s">
         <v>236</v>
       </c>
     </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A77" s="28" t="s">
+    <row r="77" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A77" s="26" t="s">
         <v>75</v>
       </c>
-      <c r="B77" s="28" t="s">
+      <c r="B77" s="26" t="s">
         <v>237</v>
       </c>
-      <c r="C77" s="28" t="s">
+      <c r="C77" s="26" t="s">
         <v>237</v>
       </c>
     </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A78" s="28" t="s">
+    <row r="78" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A78" s="26" t="s">
         <v>75</v>
       </c>
-      <c r="B78" s="28" t="s">
+      <c r="B78" s="26" t="s">
         <v>238</v>
       </c>
-      <c r="C78" s="28" t="s">
+      <c r="C78" s="26" t="s">
         <v>238</v>
       </c>
     </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A79" s="28" t="s">
+    <row r="79" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A79" s="26" t="s">
         <v>75</v>
       </c>
-      <c r="B79" s="28" t="s">
-        <v>79</v>
-      </c>
-      <c r="C79" s="28" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A80" s="28" t="s">
+      <c r="B79" s="26" t="s">
+        <v>79</v>
+      </c>
+      <c r="C79" s="26" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A80" s="26" t="s">
         <v>86</v>
       </c>
-      <c r="B80" s="28" t="s">
+      <c r="B80" s="26" t="s">
         <v>239</v>
       </c>
-      <c r="C80" s="28" t="s">
+      <c r="C80" s="26" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A81" s="28" t="s">
+    <row r="81" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A81" s="26" t="s">
         <v>86</v>
       </c>
-      <c r="B81" s="28" t="s">
+      <c r="B81" s="26" t="s">
         <v>239</v>
       </c>
-      <c r="C81" s="28" t="s">
+      <c r="C81" s="26" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A82" s="28" t="s">
+    <row r="82" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A82" s="26" t="s">
         <v>86</v>
       </c>
-      <c r="B82" s="28" t="s">
+      <c r="B82" s="26" t="s">
         <v>242</v>
       </c>
-      <c r="C82" s="28" t="s">
+      <c r="C82" s="26" t="s">
         <v>243</v>
       </c>
     </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A83" s="28" t="s">
+    <row r="83" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A83" s="26" t="s">
         <v>86</v>
       </c>
-      <c r="B83" s="28" t="s">
+      <c r="B83" s="26" t="s">
         <v>242</v>
       </c>
-      <c r="C83" s="28" t="s">
+      <c r="C83" s="26" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A84" s="28" t="s">
+    <row r="84" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A84" s="26" t="s">
         <v>86</v>
       </c>
-      <c r="B84" s="28" t="s">
-        <v>79</v>
-      </c>
-      <c r="C84" s="28" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A85" s="28" t="s">
+      <c r="B84" s="26" t="s">
+        <v>79</v>
+      </c>
+      <c r="C84" s="26" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A85" s="26" t="s">
         <v>85</v>
       </c>
-      <c r="B85" s="28" t="s">
+      <c r="B85" s="26" t="s">
         <v>245</v>
       </c>
-      <c r="C85" s="28" t="s">
+      <c r="C85" s="26" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A86" s="28" t="s">
+    <row r="86" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A86" s="26" t="s">
         <v>85</v>
       </c>
-      <c r="B86" s="28" t="s">
+      <c r="B86" s="26" t="s">
         <v>245</v>
       </c>
-      <c r="C86" s="28" t="s">
+      <c r="C86" s="26" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A87" s="28" t="s">
+    <row r="87" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A87" s="26" t="s">
         <v>85</v>
       </c>
-      <c r="B87" s="28" t="s">
+      <c r="B87" s="26" t="s">
         <v>245</v>
       </c>
-      <c r="C87" s="28" t="s">
+      <c r="C87" s="26" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A88" s="28" t="s">
+    <row r="88" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A88" s="26" t="s">
         <v>85</v>
       </c>
-      <c r="B88" s="28" t="s">
+      <c r="B88" s="26" t="s">
         <v>247</v>
       </c>
-      <c r="C88" s="28" t="s">
+      <c r="C88" s="26" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A89" s="28" t="s">
+    <row r="89" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A89" s="26" t="s">
         <v>85</v>
       </c>
-      <c r="B89" s="28" t="s">
+      <c r="B89" s="26" t="s">
         <v>247</v>
       </c>
-      <c r="C89" s="28" t="s">
+      <c r="C89" s="26" t="s">
         <v>248</v>
       </c>
     </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A90" s="28" t="s">
+    <row r="90" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A90" s="26" t="s">
         <v>85</v>
       </c>
-      <c r="B90" s="28" t="s">
+      <c r="B90" s="26" t="s">
         <v>247</v>
       </c>
-      <c r="C90" s="28" t="s">
+      <c r="C90" s="26" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A91" s="28" t="s">
+    <row r="91" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A91" s="26" t="s">
         <v>85</v>
       </c>
-      <c r="B91" s="28" t="s">
-        <v>79</v>
-      </c>
-      <c r="C91" s="28" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A92" s="28" t="s">
+      <c r="B91" s="26" t="s">
+        <v>79</v>
+      </c>
+      <c r="C91" s="26" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A92" s="26" t="s">
         <v>153</v>
       </c>
-      <c r="B92" s="28" t="s">
+      <c r="B92" s="26" t="s">
         <v>249</v>
       </c>
-      <c r="C92" s="28" t="s">
+      <c r="C92" s="26" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A93" s="28" t="s">
+    <row r="93" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A93" s="26" t="s">
         <v>153</v>
       </c>
-      <c r="B93" s="28" t="s">
+      <c r="B93" s="26" t="s">
         <v>250</v>
       </c>
-      <c r="C93" s="28" t="s">
+      <c r="C93" s="26" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A94" s="28" t="s">
+    <row r="94" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A94" s="26" t="s">
         <v>153</v>
       </c>
-      <c r="B94" s="28" t="s">
+      <c r="B94" s="26" t="s">
         <v>251</v>
       </c>
-      <c r="C94" s="28" t="s">
+      <c r="C94" s="26" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A95" s="28" t="s">
+    <row r="95" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A95" s="26" t="s">
         <v>153</v>
       </c>
-      <c r="B95" s="28" t="s">
+      <c r="B95" s="26" t="s">
         <v>251</v>
       </c>
-      <c r="C95" s="28" t="s">
+      <c r="C95" s="26" t="s">
         <v>252</v>
       </c>
     </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A96" s="28" t="s">
+    <row r="96" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A96" s="26" t="s">
         <v>153</v>
       </c>
-      <c r="B96" s="28" t="s">
+      <c r="B96" s="26" t="s">
         <v>251</v>
       </c>
-      <c r="C96" s="28" t="s">
+      <c r="C96" s="26" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A97" s="28" t="s">
+    <row r="97" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A97" s="26" t="s">
         <v>153</v>
       </c>
-      <c r="B97" s="28" t="s">
+      <c r="B97" s="26" t="s">
         <v>251</v>
       </c>
-      <c r="C97" s="28" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A98" s="28" t="s">
+      <c r="C97" s="26" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A98" s="26" t="s">
         <v>153</v>
       </c>
-      <c r="B98" s="28" t="s">
-        <v>79</v>
-      </c>
-      <c r="C98" s="28" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A99" s="28" t="s">
+      <c r="B98" s="26" t="s">
+        <v>79</v>
+      </c>
+      <c r="C98" s="26" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A99" s="26" t="s">
         <v>154</v>
       </c>
-      <c r="B99" s="28" t="s">
+      <c r="B99" s="26" t="s">
         <v>254</v>
       </c>
-      <c r="C99" s="28" t="s">
+      <c r="C99" s="26" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A100" s="28" t="s">
+    <row r="100" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A100" s="26" t="s">
         <v>154</v>
       </c>
-      <c r="B100" s="28" t="s">
+      <c r="B100" s="26" t="s">
         <v>255</v>
       </c>
-      <c r="C100" s="28" t="s">
+      <c r="C100" s="26" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A101" s="28" t="s">
+    <row r="101" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A101" s="26" t="s">
         <v>154</v>
       </c>
-      <c r="B101" s="28" t="s">
+      <c r="B101" s="26" t="s">
         <v>256</v>
       </c>
-      <c r="C101" s="28" t="s">
+      <c r="C101" s="26" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A102" s="28" t="s">
+    <row r="102" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A102" s="26" t="s">
         <v>154</v>
       </c>
-      <c r="B102" s="28" t="s">
-        <v>79</v>
-      </c>
-      <c r="C102" s="28" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A103" s="28" t="s">
-        <v>79</v>
-      </c>
-      <c r="B103" s="28" t="s">
-        <v>79</v>
-      </c>
-      <c r="C103" s="28" t="s">
+      <c r="B102" s="26" t="s">
+        <v>79</v>
+      </c>
+      <c r="C102" s="26" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A103" s="26" t="s">
+        <v>79</v>
+      </c>
+      <c r="B103" s="26" t="s">
+        <v>79</v>
+      </c>
+      <c r="C103" s="26" t="s">
         <v>79</v>
       </c>
     </row>
@@ -6686,592 +7284,592 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D785B8F3-0A92-475D-AD83-C65ACDAFA057}">
   <dimension ref="A1:C53"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="17.81640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.77734375" bestFit="1" customWidth="1"/>
     <col min="2" max="3" width="29" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A1" s="29" t="s">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="27" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="30" t="s">
+      <c r="B1" s="28" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="30" t="s">
+      <c r="C1" s="28" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A2" s="23" t="s">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" s="21" t="s">
         <v>116</v>
       </c>
-      <c r="B2" s="24" t="s">
+      <c r="B2" s="22" t="s">
         <v>117</v>
       </c>
-      <c r="C2" s="24" t="s">
+      <c r="C2" s="22" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A3" s="23" t="s">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" s="21" t="s">
         <v>116</v>
       </c>
-      <c r="B3" s="24" t="s">
+      <c r="B3" s="22" t="s">
         <v>119</v>
       </c>
-      <c r="C3" s="24" t="s">
+      <c r="C3" s="22" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A4" s="23" t="s">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" s="21" t="s">
         <v>116</v>
       </c>
-      <c r="B4" s="24" t="s">
+      <c r="B4" s="22" t="s">
         <v>257</v>
       </c>
-      <c r="C4" s="24" t="s">
+      <c r="C4" s="22" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A5" s="23" t="s">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" s="21" t="s">
         <v>84</v>
       </c>
-      <c r="B5" s="24" t="s">
+      <c r="B5" s="22" t="s">
         <v>233</v>
       </c>
-      <c r="C5" s="24" t="s">
+      <c r="C5" s="22" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A6" s="23" t="s">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" s="21" t="s">
         <v>84</v>
       </c>
-      <c r="B6" s="24" t="s">
+      <c r="B6" s="22" t="s">
         <v>234</v>
       </c>
-      <c r="C6" s="24" t="s">
+      <c r="C6" s="22" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A7" s="23" t="s">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" s="21" t="s">
         <v>84</v>
       </c>
-      <c r="B7" s="24" t="s">
-        <v>79</v>
-      </c>
-      <c r="C7" s="24" t="s">
+      <c r="B7" s="22" t="s">
+        <v>79</v>
+      </c>
+      <c r="C7" s="22" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A8" s="23" t="s">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" s="21" t="s">
         <v>75</v>
       </c>
-      <c r="B8" s="24" t="s">
+      <c r="B8" s="22" t="s">
         <v>258</v>
       </c>
-      <c r="C8" s="24" t="s">
+      <c r="C8" s="22" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A9" s="23" t="s">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" s="21" t="s">
         <v>75</v>
       </c>
-      <c r="B9" s="24" t="s">
+      <c r="B9" s="22" t="s">
         <v>125</v>
       </c>
-      <c r="C9" s="24" t="s">
+      <c r="C9" s="22" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A10" s="23" t="s">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" s="21" t="s">
         <v>75</v>
       </c>
-      <c r="B10" s="24" t="s">
+      <c r="B10" s="22" t="s">
         <v>257</v>
       </c>
-      <c r="C10" s="24" t="s">
+      <c r="C10" s="22" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A11" s="23" t="s">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" s="21" t="s">
         <v>259</v>
       </c>
-      <c r="B11" s="24" t="s">
+      <c r="B11" s="22" t="s">
         <v>260</v>
       </c>
-      <c r="C11" s="24" t="s">
+      <c r="C11" s="22" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A12" s="23" t="s">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" s="21" t="s">
         <v>259</v>
       </c>
-      <c r="B12" s="24" t="s">
+      <c r="B12" s="22" t="s">
         <v>257</v>
       </c>
-      <c r="C12" s="24" t="s">
+      <c r="C12" s="22" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A13" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="B13" s="24" t="s">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13" s="21" t="s">
+        <v>4</v>
+      </c>
+      <c r="B13" s="22" t="s">
         <v>261</v>
       </c>
-      <c r="C13" s="24" t="s">
+      <c r="C13" s="22" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A14" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="B14" s="24" t="s">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14" s="21" t="s">
+        <v>4</v>
+      </c>
+      <c r="B14" s="22" t="s">
         <v>261</v>
       </c>
-      <c r="C14" s="24" t="s">
+      <c r="C14" s="22" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A15" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="B15" s="24" t="s">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A15" s="21" t="s">
+        <v>4</v>
+      </c>
+      <c r="B15" s="22" t="s">
         <v>261</v>
       </c>
-      <c r="C15" s="24" t="s">
+      <c r="C15" s="22" t="s">
         <v>264</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A16" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="B16" s="24" t="s">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A16" s="21" t="s">
+        <v>4</v>
+      </c>
+      <c r="B16" s="22" t="s">
         <v>261</v>
       </c>
-      <c r="C16" s="24" t="s">
+      <c r="C16" s="22" t="s">
         <v>265</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A17" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="B17" s="24" t="s">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A17" s="21" t="s">
+        <v>4</v>
+      </c>
+      <c r="B17" s="22" t="s">
         <v>261</v>
       </c>
-      <c r="C17" s="24" t="s">
+      <c r="C17" s="22" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A18" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="B18" s="24" t="s">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A18" s="21" t="s">
+        <v>4</v>
+      </c>
+      <c r="B18" s="22" t="s">
         <v>261</v>
       </c>
-      <c r="C18" s="24" t="s">
+      <c r="C18" s="22" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A19" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="B19" s="24" t="s">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A19" s="21" t="s">
+        <v>4</v>
+      </c>
+      <c r="B19" s="22" t="s">
         <v>261</v>
       </c>
-      <c r="C19" s="24" t="s">
+      <c r="C19" s="22" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A20" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="B20" s="24" t="s">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A20" s="21" t="s">
+        <v>4</v>
+      </c>
+      <c r="B20" s="22" t="s">
         <v>261</v>
       </c>
-      <c r="C20" s="24" t="s">
+      <c r="C20" s="22" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A21" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="B21" s="24" t="s">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A21" s="21" t="s">
+        <v>4</v>
+      </c>
+      <c r="B21" s="22" t="s">
         <v>87</v>
       </c>
-      <c r="C21" s="24" t="s">
+      <c r="C21" s="22" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A22" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="B22" s="24" t="s">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A22" s="21" t="s">
+        <v>4</v>
+      </c>
+      <c r="B22" s="22" t="s">
         <v>87</v>
       </c>
-      <c r="C22" s="24" t="s">
+      <c r="C22" s="22" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A23" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="B23" s="24" t="s">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A23" s="21" t="s">
+        <v>4</v>
+      </c>
+      <c r="B23" s="22" t="s">
         <v>87</v>
       </c>
-      <c r="C23" s="24" t="s">
+      <c r="C23" s="22" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A24" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="B24" s="24" t="s">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A24" s="21" t="s">
+        <v>4</v>
+      </c>
+      <c r="B24" s="22" t="s">
         <v>87</v>
       </c>
-      <c r="C24" s="24" t="s">
+      <c r="C24" s="22" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A25" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="B25" s="24" t="s">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A25" s="21" t="s">
+        <v>4</v>
+      </c>
+      <c r="B25" s="22" t="s">
         <v>87</v>
       </c>
-      <c r="C25" s="24" t="s">
+      <c r="C25" s="22" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A26" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="B26" s="24" t="s">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A26" s="21" t="s">
+        <v>4</v>
+      </c>
+      <c r="B26" s="22" t="s">
         <v>87</v>
       </c>
-      <c r="C26" s="24" t="s">
+      <c r="C26" s="22" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A27" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="B27" s="24" t="s">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A27" s="21" t="s">
+        <v>4</v>
+      </c>
+      <c r="B27" s="22" t="s">
         <v>266</v>
       </c>
-      <c r="C27" s="24" t="s">
+      <c r="C27" s="22" t="s">
         <v>267</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A28" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="B28" s="24" t="s">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A28" s="21" t="s">
+        <v>4</v>
+      </c>
+      <c r="B28" s="22" t="s">
         <v>266</v>
       </c>
-      <c r="C28" s="24" t="s">
+      <c r="C28" s="22" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A29" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="B29" s="24" t="s">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A29" s="21" t="s">
+        <v>4</v>
+      </c>
+      <c r="B29" s="22" t="s">
         <v>266</v>
       </c>
-      <c r="C29" s="24" t="s">
+      <c r="C29" s="22" t="s">
         <v>268</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A30" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="B30" s="24" t="s">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A30" s="21" t="s">
+        <v>4</v>
+      </c>
+      <c r="B30" s="22" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="24" t="s">
+      <c r="C30" s="22" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A31" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="B31" s="24" t="s">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A31" s="21" t="s">
+        <v>4</v>
+      </c>
+      <c r="B31" s="22" t="s">
         <v>111</v>
       </c>
-      <c r="C31" s="24" t="s">
+      <c r="C31" s="22" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A32" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="B32" s="24" t="s">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A32" s="21" t="s">
+        <v>4</v>
+      </c>
+      <c r="B32" s="22" t="s">
         <v>111</v>
       </c>
-      <c r="C32" s="24" t="s">
+      <c r="C32" s="22" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A33" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="B33" s="24" t="s">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A33" s="21" t="s">
+        <v>4</v>
+      </c>
+      <c r="B33" s="22" t="s">
         <v>111</v>
       </c>
-      <c r="C33" s="24" t="s">
+      <c r="C33" s="22" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A34" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="B34" s="24" t="s">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A34" s="21" t="s">
+        <v>4</v>
+      </c>
+      <c r="B34" s="22" t="s">
         <v>111</v>
       </c>
-      <c r="C34" s="24" t="s">
+      <c r="C34" s="22" t="s">
         <v>269</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A35" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="B35" s="24" t="s">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A35" s="21" t="s">
+        <v>4</v>
+      </c>
+      <c r="B35" s="22" t="s">
         <v>111</v>
       </c>
-      <c r="C35" s="24" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A36" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="B36" s="25" t="s">
+      <c r="C35" s="22" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A36" s="21" t="s">
+        <v>4</v>
+      </c>
+      <c r="B36" s="23" t="s">
         <v>15</v>
       </c>
-      <c r="C36" s="25" t="s">
+      <c r="C36" s="23" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A37" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="B37" s="25" t="s">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A37" s="21" t="s">
+        <v>4</v>
+      </c>
+      <c r="B37" s="23" t="s">
         <v>257</v>
       </c>
-      <c r="C37" s="25" t="s">
+      <c r="C37" s="23" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A38" s="23" t="s">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A38" s="21" t="s">
         <v>270</v>
       </c>
-      <c r="B38" s="24" t="s">
+      <c r="B38" s="22" t="s">
         <v>271</v>
       </c>
-      <c r="C38" s="24" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A39" s="23" t="s">
+      <c r="C38" s="22" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A39" s="21" t="s">
         <v>270</v>
       </c>
-      <c r="B39" s="24" t="s">
+      <c r="B39" s="22" t="s">
         <v>272</v>
       </c>
-      <c r="C39" s="24" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A40" s="23" t="s">
+      <c r="C39" s="22" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A40" s="21" t="s">
         <v>270</v>
       </c>
-      <c r="B40" s="24" t="s">
+      <c r="B40" s="22" t="s">
         <v>254</v>
       </c>
-      <c r="C40" s="24" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A41" s="23" t="s">
+      <c r="C40" s="22" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A41" s="21" t="s">
         <v>270</v>
       </c>
-      <c r="B41" s="24" t="s">
+      <c r="B41" s="22" t="s">
         <v>273</v>
       </c>
-      <c r="C41" s="24" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A42" s="23" t="s">
+      <c r="C41" s="22" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A42" s="21" t="s">
         <v>270</v>
       </c>
-      <c r="B42" s="25" t="s">
+      <c r="B42" s="23" t="s">
         <v>257</v>
       </c>
-      <c r="C42" s="25" t="s">
+      <c r="C42" s="23" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A43" s="23" t="s">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A43" s="21" t="s">
         <v>274</v>
       </c>
-      <c r="B43" s="24" t="s">
+      <c r="B43" s="22" t="s">
         <v>189</v>
       </c>
-      <c r="C43" s="24" t="s">
+      <c r="C43" s="22" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A44" s="23" t="s">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A44" s="21" t="s">
         <v>274</v>
       </c>
-      <c r="B44" s="24" t="s">
+      <c r="B44" s="22" t="s">
         <v>189</v>
       </c>
-      <c r="C44" s="24" t="s">
+      <c r="C44" s="22" t="s">
         <v>275</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A45" s="23" t="s">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A45" s="21" t="s">
         <v>274</v>
       </c>
-      <c r="B45" s="24" t="s">
+      <c r="B45" s="22" t="s">
         <v>189</v>
       </c>
-      <c r="C45" s="24" t="s">
+      <c r="C45" s="22" t="s">
         <v>276</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A46" s="23" t="s">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A46" s="21" t="s">
         <v>274</v>
       </c>
-      <c r="B46" s="24" t="s">
+      <c r="B46" s="22" t="s">
         <v>189</v>
       </c>
-      <c r="C46" s="24" t="s">
+      <c r="C46" s="22" t="s">
         <v>277</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A47" s="23" t="s">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A47" s="21" t="s">
         <v>274</v>
       </c>
-      <c r="B47" s="24" t="s">
+      <c r="B47" s="22" t="s">
         <v>187</v>
       </c>
-      <c r="C47" s="24" t="s">
+      <c r="C47" s="22" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A48" s="23" t="s">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A48" s="21" t="s">
         <v>274</v>
       </c>
-      <c r="B48" s="24" t="s">
+      <c r="B48" s="22" t="s">
         <v>278</v>
       </c>
-      <c r="C48" s="24" t="s">
+      <c r="C48" s="22" t="s">
         <v>278</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A49" s="23" t="s">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A49" s="21" t="s">
         <v>274</v>
       </c>
-      <c r="B49" s="25" t="s">
+      <c r="B49" s="23" t="s">
         <v>257</v>
       </c>
-      <c r="C49" s="25" t="s">
+      <c r="C49" s="23" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A50" s="23" t="s">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A50" s="21" t="s">
         <v>85</v>
       </c>
-      <c r="B50" s="24" t="s">
+      <c r="B50" s="22" t="s">
         <v>279</v>
       </c>
-      <c r="C50" s="24" t="s">
+      <c r="C50" s="22" t="s">
         <v>280</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A51" s="23" t="s">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A51" s="21" t="s">
         <v>85</v>
       </c>
-      <c r="B51" s="24" t="s">
+      <c r="B51" s="22" t="s">
         <v>279</v>
       </c>
-      <c r="C51" s="24" t="s">
+      <c r="C51" s="22" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A52" s="23" t="s">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A52" s="21" t="s">
         <v>85</v>
       </c>
-      <c r="B52" s="24" t="s">
+      <c r="B52" s="22" t="s">
         <v>281</v>
       </c>
-      <c r="C52" s="24" t="s">
+      <c r="C52" s="22" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A53" s="23" t="s">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A53" s="21" t="s">
         <v>85</v>
       </c>
-      <c r="B53" s="25" t="s">
+      <c r="B53" s="23" t="s">
         <v>257</v>
       </c>
-      <c r="C53" s="25" t="s">
+      <c r="C53" s="23" t="s">
         <v>257</v>
       </c>
     </row>
